--- a/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
+++ b/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/007_POLIMO_CHAMPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FF69B8-A410-694E-9A36-92F794F6F21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2B9BAE-5850-CF4C-AB09-33DAE70A9947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -788,16 +788,37 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -812,34 +833,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -858,9 +861,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,23 +1276,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="49"/>
+      <c r="A2" s="56"/>
     </row>
     <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
+      <c r="A3" s="56"/>
     </row>
     <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="56" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="49"/>
+      <c r="A5" s="56"/>
     </row>
     <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1330,12 +1330,12 @@
       </c>
     </row>
     <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="57" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="50"/>
+      <c r="A14" s="57"/>
     </row>
     <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1363,12 +1363,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="56" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="49"/>
+      <c r="A21" s="56"/>
     </row>
     <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -1424,13 +1424,13 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="56" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="49"/>
+      <c r="A33" s="56"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1493,12 +1493,12 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="56" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="49"/>
+      <c r="A45" s="56"/>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1562,12 +1562,12 @@
       <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="49" t="s">
+      <c r="A56" s="56" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="49"/>
+      <c r="A57" s="56"/>
       <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1685,17 +1685,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -2707,36 +2707,36 @@
       <c r="AMG1" s="31"/>
     </row>
     <row r="2" spans="1:1021" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
-      <c r="L3" s="62"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="52"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="31"/>
@@ -3748,26 +3748,26 @@
       <c r="AMG3" s="31"/>
     </row>
     <row r="4" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="21"/>
@@ -5094,20 +5094,20 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="31"/>
@@ -6119,26 +6119,26 @@
       <c r="AMG22" s="31"/>
     </row>
     <row r="23" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="53" t="s">
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53" t="s">
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
@@ -7463,20 +7463,20 @@
       <c r="L40" s="24"/>
     </row>
     <row r="41" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
       <c r="M41" s="31"/>
       <c r="N41" s="31"/>
       <c r="O41" s="31"/>
@@ -8488,26 +8488,26 @@
       <c r="AMG41" s="31"/>
     </row>
     <row r="42" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="53" t="s">
+      <c r="B42" s="48"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53" t="s">
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="53"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53" t="s">
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
@@ -9834,20 +9834,20 @@
       <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A60" s="66" t="s">
+      <c r="A60" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="66"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="66"/>
-      <c r="L60" s="66"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="67"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="67"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="67"/>
       <c r="M60" s="31"/>
       <c r="N60" s="31"/>
       <c r="O60" s="31"/>
@@ -10859,26 +10859,26 @@
       <c r="AMG60" s="31"/>
     </row>
     <row r="61" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="55"/>
-      <c r="C61" s="56"/>
-      <c r="D61" s="53" t="s">
+      <c r="B61" s="48"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53" t="s">
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="53"/>
-      <c r="I61" s="53"/>
-      <c r="J61" s="53" t="s">
+      <c r="H61" s="46"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="53"/>
-      <c r="L61" s="53"/>
+      <c r="K61" s="46"/>
+      <c r="L61" s="46"/>
       <c r="M61" s="31"/>
       <c r="N61" s="31"/>
       <c r="O61" s="31"/>
@@ -12249,63 +12249,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="66"/>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="52"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="49"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -12509,34 +12509,34 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="62"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="52"/>
     </row>
     <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="54" t="s">
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="55"/>
-      <c r="I15" s="56"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="49"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
@@ -12740,34 +12740,34 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53" t="s">
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="54" t="s">
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="49"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
@@ -12971,34 +12971,34 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A36" s="60" t="s">
+      <c r="A36" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="62"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="52"/>
     </row>
     <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53" t="s">
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="54" t="s">
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="49"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
@@ -13238,12 +13238,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
     </row>
     <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
@@ -14298,12 +14298,12 @@
       <c r="AMJ3" s="10"/>
     </row>
     <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -15372,12 +15372,12 @@
       <c r="AMJ6" s="10"/>
     </row>
     <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -16446,12 +16446,12 @@
       <c r="AMJ9" s="10"/>
     </row>
     <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -17526,12 +17526,12 @@
       <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -17974,12 +17974,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="63"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18027,12 +18027,12 @@
       <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="48"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
@@ -18077,12 +18077,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -18136,12 +18136,12 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="48"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -18204,12 +18204,12 @@
       <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -18220,12 +18220,12 @@
       <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -18682,12 +18682,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="63"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18774,12 +18774,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
@@ -18860,12 +18860,12 @@
       <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="63"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -18957,12 +18957,12 @@
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="63"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -19065,12 +19065,12 @@
       <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -19081,12 +19081,12 @@
       <c r="O26" s="10"/>
     </row>
     <row r="27" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -19553,61 +19553,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="59"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="55"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54" t="s">
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="54" t="s">
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="55"/>
-      <c r="M3" s="56"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -19652,82 +19652,58 @@
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="69">
-        <v>0.10589900049000001</v>
-      </c>
-      <c r="C5" s="69">
-        <v>9.6496928455000006E-2</v>
-      </c>
-      <c r="D5" s="69">
-        <v>9.1363299006999993E-3</v>
-      </c>
-      <c r="E5" s="11">
-        <v>0.11307017424</v>
-      </c>
-      <c r="F5" s="11">
-        <v>0.10091046316000001</v>
-      </c>
-      <c r="G5" s="11">
-        <v>9.4544248220000005E-3</v>
-      </c>
-      <c r="H5" s="11">
-        <v>0.11449747231</v>
-      </c>
-      <c r="I5" s="11">
-        <v>0.10140866866999999</v>
-      </c>
-      <c r="J5" s="11">
-        <v>9.4544248220000005E-3</v>
-      </c>
-      <c r="K5" s="25">
-        <v>0.11451795777</v>
-      </c>
-      <c r="L5" s="25">
-        <v>0.1012443286</v>
-      </c>
-      <c r="M5" s="25">
-        <v>9.4544248220000005E-3</v>
-      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="52"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="54" t="s">
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="54" t="s">
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="49"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -19772,82 +19748,82 @@
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="69">
-        <v>0.10581169737</v>
-      </c>
-      <c r="C9" s="69">
-        <v>9.6430921853000007E-2</v>
-      </c>
-      <c r="D9" s="69">
-        <v>8.9220420089000003E-3</v>
+      <c r="B9" s="45">
+        <v>0.10601687326000001</v>
+      </c>
+      <c r="C9" s="45">
+        <v>9.9404248786999994E-2</v>
+      </c>
+      <c r="D9" s="45">
+        <v>3.4736236120000001E-3</v>
       </c>
       <c r="E9" s="11">
-        <v>0.11306479073</v>
+        <v>0.11321899581</v>
       </c>
       <c r="F9" s="11">
-        <v>0.10094761708</v>
+        <v>0.10303987420000001</v>
       </c>
       <c r="G9" s="11">
-        <v>9.2386319384000007E-3</v>
+        <v>3.0526982389999999E-3</v>
       </c>
       <c r="H9" s="11">
-        <v>0.11451281345</v>
+        <v>0.11465817699</v>
       </c>
       <c r="I9" s="11">
-        <v>0.10145940022</v>
+        <v>0.10358621039</v>
       </c>
       <c r="J9" s="11">
-        <v>9.3786239800000004E-3</v>
+        <v>3.0526982389999999E-3</v>
       </c>
       <c r="K9" s="25">
-        <v>0.11452431192</v>
+        <v>0.11466144163</v>
       </c>
       <c r="L9" s="25">
-        <v>0.10129881402</v>
+        <v>0.10343307147</v>
       </c>
       <c r="M9" s="25">
-        <v>9.2386319384000007E-3</v>
+        <v>3.0526982389999999E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="54" t="s">
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="55"/>
-      <c r="M11" s="56"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="49"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -19892,82 +19868,82 @@
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="69">
-        <v>0.10596296252</v>
-      </c>
-      <c r="C13" s="69">
-        <v>9.639693547E-2</v>
-      </c>
-      <c r="D13" s="69">
-        <v>9.0552070479000008E-3</v>
+      <c r="B13" s="45">
+        <v>0.10617966317999999</v>
+      </c>
+      <c r="C13" s="45">
+        <v>9.9562169199000003E-2</v>
+      </c>
+      <c r="D13" s="45">
+        <v>3.3568244576999999E-3</v>
       </c>
       <c r="E13" s="11">
-        <v>0.11301167239</v>
+        <v>0.11317467214</v>
       </c>
       <c r="F13" s="11">
-        <v>0.10098052784</v>
+        <v>0.10308663434</v>
       </c>
       <c r="G13" s="11">
-        <v>9.4911747776999997E-3</v>
+        <v>2.8756702953E-3</v>
       </c>
       <c r="H13" s="11">
-        <v>0.11440413257</v>
+        <v>0.11455664271</v>
       </c>
       <c r="I13" s="38">
-        <v>0.10144898703999999</v>
+        <v>0.10356659192000001</v>
       </c>
       <c r="J13" s="38">
-        <v>9.4911747776999997E-3</v>
+        <v>2.8756702953E-3</v>
       </c>
       <c r="K13" s="25">
-        <v>0.11447150251</v>
+        <v>0.11462122683000001</v>
       </c>
       <c r="L13" s="39">
-        <v>0.10132745264</v>
+        <v>0.10348634096000001</v>
       </c>
       <c r="M13" s="39">
-        <v>9.4911747776999997E-3</v>
+        <v>2.8756702953E-3</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54" t="s">
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="54" t="s">
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="55"/>
-      <c r="M15" s="56"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -20012,41 +19988,41 @@
       <c r="A17" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="69">
-        <v>0.10562470228</v>
-      </c>
-      <c r="C17" s="69">
-        <v>9.6133527905000002E-2</v>
-      </c>
-      <c r="D17" s="69">
-        <v>8.7514955158999996E-3</v>
+      <c r="B17" s="45">
+        <v>0.10600472226</v>
+      </c>
+      <c r="C17" s="45">
+        <v>9.9522119766999997E-2</v>
+      </c>
+      <c r="D17" s="45">
+        <v>3.3685456435999998E-3</v>
       </c>
       <c r="E17" s="11">
-        <v>0.11291503467</v>
+        <v>0.11323210886</v>
       </c>
       <c r="F17" s="11">
-        <v>0.10134847875</v>
+        <v>0.10317312774</v>
       </c>
       <c r="G17" s="11">
-        <v>9.2883567175999996E-3</v>
+        <v>3.3685456435999998E-3</v>
       </c>
       <c r="H17" s="11">
-        <v>0.11428590415000001</v>
+        <v>0.1145998419</v>
       </c>
       <c r="I17" s="11">
-        <v>0.10181878373</v>
+        <v>0.10371447941</v>
       </c>
       <c r="J17" s="11">
-        <v>9.2883567175999996E-3</v>
+        <v>2.4493230975E-3</v>
       </c>
       <c r="K17" s="11">
-        <v>0.11434853053000001</v>
+        <v>0.11467426321</v>
       </c>
       <c r="L17" s="11">
-        <v>0.10172434843</v>
+        <v>0.10364270271000001</v>
       </c>
       <c r="M17" s="11">
-        <v>9.2883567175999996E-3</v>
+        <v>2.4493230975E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20099,74 +20075,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
     </row>
     <row r="2" spans="1:17" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
     </row>
     <row r="4" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
@@ -20214,36 +20190,28 @@
       <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="11">
-        <v>0.10589900049000001</v>
-      </c>
+      <c r="B6" s="11"/>
       <c r="C6" s="19">
         <v>20</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="11">
-        <v>3.5906143085999999E-3</v>
-      </c>
+      <c r="E6" s="11"/>
       <c r="F6" s="19">
         <v>7.3890000000000002</v>
       </c>
       <c r="G6" s="19">
         <v>1</v>
       </c>
-      <c r="H6" s="11">
-        <v>6.922351916E-4</v>
-      </c>
+      <c r="H6" s="11"/>
       <c r="I6" s="22">
         <v>5.6689999999999996</v>
       </c>
       <c r="J6" s="19">
         <v>1</v>
       </c>
-      <c r="K6" s="11">
-        <v>6.922351916E-4</v>
-      </c>
+      <c r="K6" s="11"/>
       <c r="L6" s="19">
         <v>5.6689999999999996</v>
       </c>
@@ -20256,27 +20224,21 @@
       <c r="D7" s="19">
         <v>2</v>
       </c>
-      <c r="E7" s="11">
-        <v>5.4659106409999998E-2</v>
-      </c>
+      <c r="E7" s="11"/>
       <c r="F7" s="19">
         <v>17.800999999999998</v>
       </c>
       <c r="G7" s="19">
         <v>2</v>
       </c>
-      <c r="H7" s="11">
-        <v>1.0395991564E-2</v>
-      </c>
+      <c r="H7" s="11"/>
       <c r="I7" s="22">
         <v>9.7479999999999993</v>
       </c>
       <c r="J7" s="19">
         <v>2</v>
       </c>
-      <c r="K7" s="11">
-        <v>6.6053596381999997E-3</v>
-      </c>
+      <c r="K7" s="11"/>
       <c r="L7" s="19">
         <v>9</v>
       </c>
@@ -20289,27 +20251,21 @@
       <c r="D8" s="19">
         <v>3</v>
       </c>
-      <c r="E8" s="40">
-        <v>5.4820453525999999E-2</v>
-      </c>
+      <c r="E8" s="40"/>
       <c r="F8" s="19">
         <v>47.457999999999998</v>
       </c>
       <c r="G8" s="19">
         <v>3</v>
       </c>
-      <c r="H8" s="11">
-        <v>1.8790759301999999E-2</v>
-      </c>
+      <c r="H8" s="11"/>
       <c r="I8" s="22">
         <v>16.962</v>
       </c>
       <c r="J8" s="19">
         <v>3</v>
       </c>
-      <c r="K8" s="11">
-        <v>7.3326355458000004E-3</v>
-      </c>
+      <c r="K8" s="11"/>
       <c r="L8" s="19">
         <v>12.718999999999999</v>
       </c>
@@ -20325,18 +20281,14 @@
       <c r="G9" s="19">
         <v>4</v>
       </c>
-      <c r="H9" s="11">
-        <v>2.8642013168999999E-2</v>
-      </c>
+      <c r="H9" s="11"/>
       <c r="I9" s="22">
         <v>26.009</v>
       </c>
       <c r="J9" s="19">
         <v>4</v>
       </c>
-      <c r="K9" s="11">
-        <v>9.9715073729999999E-3</v>
-      </c>
+      <c r="K9" s="11"/>
       <c r="L9" s="19">
         <v>16.966000000000001</v>
       </c>
@@ -20351,18 +20303,14 @@
       <c r="G10" s="19">
         <v>5</v>
       </c>
-      <c r="H10" s="11">
-        <v>3.4971503855000002E-2</v>
-      </c>
+      <c r="H10" s="11"/>
       <c r="I10" s="22">
         <v>41.75</v>
       </c>
       <c r="J10" s="19">
         <v>5</v>
       </c>
-      <c r="K10" s="11">
-        <v>1.0405327420999999E-2</v>
-      </c>
+      <c r="K10" s="11"/>
       <c r="L10" s="19">
         <v>20.881</v>
       </c>
@@ -20377,18 +20325,14 @@
       <c r="G11" s="19">
         <v>6</v>
       </c>
-      <c r="H11" s="11">
-        <v>1.8678554856E-2</v>
-      </c>
+      <c r="H11" s="11"/>
       <c r="I11" s="22">
         <v>72.683000000000007</v>
       </c>
       <c r="J11" s="19">
         <v>6</v>
       </c>
-      <c r="K11" s="11">
-        <v>1.0650501087000001E-2</v>
-      </c>
+      <c r="K11" s="11"/>
       <c r="L11" s="19">
         <v>24.969000000000001</v>
       </c>
@@ -20403,18 +20347,14 @@
       <c r="G12" s="19">
         <v>7</v>
       </c>
-      <c r="H12" s="11">
-        <v>2.3264143750999998E-3</v>
-      </c>
+      <c r="H12" s="11"/>
       <c r="I12" s="22">
         <v>149.39099999999999</v>
       </c>
       <c r="J12" s="19">
         <v>7</v>
       </c>
-      <c r="K12" s="11">
-        <v>9.0831398986000005E-3</v>
-      </c>
+      <c r="K12" s="11"/>
       <c r="L12" s="19">
         <v>28.847999999999999</v>
       </c>
@@ -20432,9 +20372,7 @@
       <c r="J13" s="19">
         <v>8</v>
       </c>
-      <c r="K13" s="11">
-        <v>8.1033328622000002E-3</v>
-      </c>
+      <c r="K13" s="11"/>
       <c r="L13" s="19">
         <v>33.03</v>
       </c>
@@ -20452,9 +20390,7 @@
       <c r="J14" s="19">
         <v>9</v>
       </c>
-      <c r="K14" s="11">
-        <v>7.1542989369000002E-3</v>
-      </c>
+      <c r="K14" s="11"/>
       <c r="L14" s="19">
         <v>36.945</v>
       </c>
@@ -20472,9 +20408,7 @@
       <c r="J15" s="19">
         <v>10</v>
       </c>
-      <c r="K15" s="11">
-        <v>7.0638179327999996E-3</v>
-      </c>
+      <c r="K15" s="11"/>
       <c r="L15" s="19">
         <v>40.929000000000002</v>
       </c>
@@ -20492,9 +20426,7 @@
       <c r="J16" s="19">
         <v>11</v>
       </c>
-      <c r="K16" s="11">
-        <v>5.4370890721000004E-3</v>
-      </c>
+      <c r="K16" s="11"/>
       <c r="L16" s="19">
         <v>44.854999999999997</v>
       </c>
@@ -20512,9 +20444,7 @@
       <c r="J17" s="19">
         <v>12</v>
       </c>
-      <c r="K17" s="11">
-        <v>1.1200528027999999E-2</v>
-      </c>
+      <c r="K17" s="11"/>
       <c r="L17" s="19">
         <v>50.978000000000002</v>
       </c>
@@ -20532,9 +20462,7 @@
       <c r="J18" s="19">
         <v>13</v>
       </c>
-      <c r="K18" s="11">
-        <v>1.2290107062E-2</v>
-      </c>
+      <c r="K18" s="11"/>
       <c r="L18" s="19">
         <v>66.174999999999997</v>
       </c>
@@ -20552,9 +20480,7 @@
       <c r="J19" s="19">
         <v>14</v>
       </c>
-      <c r="K19" s="11">
-        <v>6.2016633433E-3</v>
-      </c>
+      <c r="K19" s="11"/>
       <c r="L19" s="19">
         <v>96.876000000000005</v>
       </c>
@@ -20572,9 +20498,7 @@
       <c r="J20" s="19">
         <v>15</v>
       </c>
-      <c r="K20" s="11">
-        <v>2.3264143750999998E-3</v>
-      </c>
+      <c r="K20" s="11"/>
       <c r="L20" s="19">
         <v>149.39099999999999</v>
       </c>
@@ -20598,46 +20522,46 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
       <c r="M22" s="28"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
     </row>
     <row r="23" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53" t="s">
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53" t="s">
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
@@ -20687,7 +20611,9 @@
       <c r="A25" s="19">
         <v>1</v>
       </c>
-      <c r="B25" s="11"/>
+      <c r="B25" s="11">
+        <v>0.10601687326000001</v>
+      </c>
       <c r="C25" s="19">
         <v>20</v>
       </c>
@@ -20695,7 +20621,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="11">
-        <v>3.592729809E-3</v>
+        <v>3.6191471606999998E-3</v>
       </c>
       <c r="F25" s="20">
         <v>7.3890000000000002</v>
@@ -20704,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="11">
-        <v>6.9484073781000001E-4</v>
+        <v>7.0376567548999995E-4</v>
       </c>
       <c r="I25" s="22">
         <v>5.6689999999999996</v>
@@ -20713,7 +20639,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="11">
-        <v>6.9484073781000001E-4</v>
+        <v>7.0376567548999995E-4</v>
       </c>
       <c r="L25" s="19">
         <v>5.6689999999999996</v>
@@ -20727,7 +20653,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="11">
-        <v>5.4622181881000001E-2</v>
+        <v>5.4751361572000001E-2</v>
       </c>
       <c r="F26" s="19">
         <v>17.800999999999998</v>
@@ -20736,7 +20662,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="11">
-        <v>1.0390391590000001E-2</v>
+        <v>1.0441883743000001E-2</v>
       </c>
       <c r="I26" s="22">
         <v>9.7479999999999993</v>
@@ -20745,7 +20671,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="11">
-        <v>6.5862475017000001E-3</v>
+        <v>6.6225383302999999E-3</v>
       </c>
       <c r="L26" s="19">
         <v>9</v>
@@ -20758,8 +20684,8 @@
       <c r="D27" s="19">
         <v>3</v>
       </c>
-      <c r="E27" s="11">
-        <v>5.4849879040999999E-2</v>
+      <c r="E27" s="40">
+        <v>5.4848487075999999E-2</v>
       </c>
       <c r="F27" s="19">
         <v>47.457999999999998</v>
@@ -20768,7 +20694,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="11">
-        <v>1.8784721624000002E-2</v>
+        <v>1.8831612362E-2</v>
       </c>
       <c r="I27" s="22">
         <v>16.962</v>
@@ -20777,7 +20703,7 @@
         <v>3</v>
       </c>
       <c r="K27" s="11">
-        <v>7.3317450494000003E-3</v>
+        <v>7.3527203031999999E-3</v>
       </c>
       <c r="L27" s="19">
         <v>12.718999999999999</v>
@@ -20794,7 +20720,7 @@
         <v>4</v>
       </c>
       <c r="H28" s="11">
-        <v>2.8649210506E-2</v>
+        <v>2.8686571216999999E-2</v>
       </c>
       <c r="I28" s="22">
         <v>26.009</v>
@@ -20803,7 +20729,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="11">
-        <v>9.9683281951000006E-3</v>
+        <v>9.9932092379999993E-3</v>
       </c>
       <c r="L28" s="19">
         <v>16.966000000000001</v>
@@ -20819,7 +20745,7 @@
         <v>5</v>
       </c>
       <c r="H29" s="11">
-        <v>3.4985875504000001E-2</v>
+        <v>3.4992861857999998E-2</v>
       </c>
       <c r="I29" s="22">
         <v>41.75</v>
@@ -20828,7 +20754,7 @@
         <v>5</v>
       </c>
       <c r="K29" s="11">
-        <v>1.0407169880000001E-2</v>
+        <v>1.0426659614E-2</v>
       </c>
       <c r="L29" s="19">
         <v>20.881</v>
@@ -20844,7 +20770,7 @@
         <v>6</v>
       </c>
       <c r="H30" s="11">
-        <v>1.8680960675999999E-2</v>
+        <v>1.8675231406000001E-2</v>
       </c>
       <c r="I30" s="22">
         <v>72.683000000000007</v>
@@ -20853,7 +20779,7 @@
         <v>6</v>
       </c>
       <c r="K30" s="11">
-        <v>1.065147709E-2</v>
+        <v>1.0666488759E-2</v>
       </c>
       <c r="L30" s="19">
         <v>24.969000000000001</v>
@@ -20869,7 +20795,7 @@
         <v>7</v>
       </c>
       <c r="H31" s="11">
-        <v>2.3268128149000001E-3</v>
+        <v>2.3262507258000002E-3</v>
       </c>
       <c r="I31" s="22">
         <v>149.39099999999999</v>
@@ -20878,7 +20804,7 @@
         <v>7</v>
       </c>
       <c r="K31" s="11">
-        <v>9.0880967417000004E-3</v>
+        <v>9.0975773418000005E-3</v>
       </c>
       <c r="L31" s="19">
         <v>28.847999999999999</v>
@@ -20897,7 +20823,7 @@
         <v>8</v>
       </c>
       <c r="K32" s="11">
-        <v>8.1069682879999997E-3</v>
+        <v>8.1122896720000007E-3</v>
       </c>
       <c r="L32" s="19">
         <v>33.03</v>
@@ -20916,7 +20842,7 @@
         <v>9</v>
       </c>
       <c r="K33" s="11">
-        <v>7.1563453333000002E-3</v>
+        <v>7.1587782911000002E-3</v>
       </c>
       <c r="L33" s="19">
         <v>36.945</v>
@@ -20935,7 +20861,7 @@
         <v>10</v>
       </c>
       <c r="K34" s="11">
-        <v>7.0667780559E-3</v>
+        <v>7.0679942976000004E-3</v>
       </c>
       <c r="L34" s="19">
         <v>40.929000000000002</v>
@@ -20954,7 +20880,7 @@
         <v>11</v>
       </c>
       <c r="K35" s="11">
-        <v>5.4400323305999997E-3</v>
+        <v>5.4404178946000003E-3</v>
       </c>
       <c r="L35" s="19">
         <v>44.854999999999997</v>
@@ -20973,7 +20899,7 @@
         <v>12</v>
       </c>
       <c r="K36" s="11">
-        <v>1.1205117221E-2</v>
+        <v>1.1204406158E-2</v>
       </c>
       <c r="L36" s="19">
         <v>50.978000000000002</v>
@@ -20992,7 +20918,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="11">
-        <v>1.2291957826E-2</v>
+        <v>1.2288726890000001E-2</v>
       </c>
       <c r="L37" s="19">
         <v>66.174999999999997</v>
@@ -21011,7 +20937,7 @@
         <v>14</v>
       </c>
       <c r="K38" s="11">
-        <v>6.2023948585000002E-3</v>
+        <v>6.1996184411999998E-3</v>
       </c>
       <c r="L38" s="19">
         <v>96.876000000000005</v>
@@ -21030,7 +20956,7 @@
         <v>15</v>
       </c>
       <c r="K39" s="11">
-        <v>2.3268128149000001E-3</v>
+        <v>2.3262507258000002E-3</v>
       </c>
       <c r="L39" s="19">
         <v>149.39099999999999</v>
@@ -21053,45 +20979,45 @@
       <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
       <c r="O41" s="29"/>
       <c r="P41" s="29"/>
       <c r="Q41" s="29"/>
     </row>
     <row r="42" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53" t="s">
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53" t="s">
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="53"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53" t="s">
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -21136,7 +21062,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="11">
-        <v>0.10596296252</v>
+        <v>0.10617966317999999</v>
       </c>
       <c r="C44" s="19">
         <v>20</v>
@@ -21145,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="11">
-        <v>3.5870001208000001E-3</v>
+        <v>3.6154307402999999E-3</v>
       </c>
       <c r="F44" s="20">
         <v>7.3890000000000002</v>
@@ -21154,7 +21080,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="11">
-        <v>6.8638711137000003E-4</v>
+        <v>6.9666429138999996E-4</v>
       </c>
       <c r="I44" s="22">
         <v>5.6689999999999996</v>
@@ -21163,7 +21089,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="11">
-        <v>6.8638711137000003E-4</v>
+        <v>6.9666429138999996E-4</v>
       </c>
       <c r="L44" s="19">
         <v>5.6689999999999996</v>
@@ -21174,7 +21100,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="11">
-        <v>5.4632996725000001E-2</v>
+        <v>5.4763516233999998E-2</v>
       </c>
       <c r="F45" s="19">
         <v>17.800999999999998</v>
@@ -21183,7 +21109,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="11">
-        <v>1.0337461046E-2</v>
+        <v>1.0388740168E-2</v>
       </c>
       <c r="I45" s="22">
         <v>9.7479999999999993</v>
@@ -21192,7 +21118,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="11">
-        <v>6.5928679993999999E-3</v>
+        <v>6.6304208040999998E-3</v>
       </c>
       <c r="L45" s="19">
         <v>9</v>
@@ -21203,7 +21129,7 @@
         <v>3</v>
       </c>
       <c r="E46" s="11">
-        <v>5.4791675541E-2</v>
+        <v>5.4795725162999999E-2</v>
       </c>
       <c r="F46" s="19">
         <v>47.457999999999998</v>
@@ -21212,7 +21138,7 @@
         <v>3</v>
       </c>
       <c r="H46" s="11">
-        <v>1.8803413541E-2</v>
+        <v>1.8852026530999998E-2</v>
       </c>
       <c r="I46" s="22">
         <v>16.962</v>
@@ -21221,7 +21147,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="11">
-        <v>7.3299785430999999E-3</v>
+        <v>7.354126941E-3</v>
       </c>
       <c r="L46" s="19">
         <v>12.718999999999999</v>
@@ -21235,7 +21161,7 @@
         <v>4</v>
       </c>
       <c r="H47" s="11">
-        <v>2.8625308322000002E-2</v>
+        <v>2.8662345765E-2</v>
       </c>
       <c r="I47" s="22">
         <v>26.009</v>
@@ -21244,7 +21170,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11">
-        <v>9.9781698472999995E-3</v>
+        <v>1.0003977884000001E-2</v>
       </c>
       <c r="L47" s="19">
         <v>16.966000000000001</v>
@@ -21257,7 +21183,7 @@
         <v>5</v>
       </c>
       <c r="H48" s="11">
-        <v>3.4953352588000003E-2</v>
+        <v>3.4963536805000001E-2</v>
       </c>
       <c r="I48" s="22">
         <v>41.75</v>
@@ -21266,7 +21192,7 @@
         <v>5</v>
       </c>
       <c r="K48" s="11">
-        <v>1.0407617171E-2</v>
+        <v>1.0427624686E-2</v>
       </c>
       <c r="L48" s="19">
         <v>20.881</v>
@@ -21279,7 +21205,7 @@
         <v>6</v>
       </c>
       <c r="H49" s="11">
-        <v>1.8671632516E-2</v>
+        <v>1.8667317007999999E-2</v>
       </c>
       <c r="I49" s="22">
         <v>72.683000000000007</v>
@@ -21288,7 +21214,7 @@
         <v>6</v>
       </c>
       <c r="K49" s="11">
-        <v>1.0646853054E-2</v>
+        <v>1.0662454441E-2</v>
       </c>
       <c r="L49" s="19">
         <v>24.969000000000001</v>
@@ -21301,7 +21227,7 @@
         <v>7</v>
       </c>
       <c r="H50" s="11">
-        <v>2.3265774455E-3</v>
+        <v>2.3260121433999999E-3</v>
       </c>
       <c r="I50" s="22">
         <v>149.39099999999999</v>
@@ -21310,7 +21236,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="11">
-        <v>9.0777340654000001E-3</v>
+        <v>9.0881716574999997E-3</v>
       </c>
       <c r="L50" s="19">
         <v>28.847999999999999</v>
@@ -21326,7 +21252,7 @@
         <v>8</v>
       </c>
       <c r="K51" s="11">
-        <v>8.0985744673999997E-3</v>
+        <v>8.1040635245000006E-3</v>
       </c>
       <c r="L51" s="19">
         <v>33.03</v>
@@ -21342,7 +21268,7 @@
         <v>9</v>
       </c>
       <c r="K52" s="11">
-        <v>7.1504639758E-3</v>
+        <v>7.1538043290999996E-3</v>
       </c>
       <c r="L52" s="19">
         <v>36.945</v>
@@ -21358,7 +21284,7 @@
         <v>10</v>
       </c>
       <c r="K53" s="11">
-        <v>7.0599280904999999E-3</v>
+        <v>7.0621424643999998E-3</v>
       </c>
       <c r="L53" s="19">
         <v>40.929000000000002</v>
@@ -21374,7 +21300,7 @@
         <v>11</v>
       </c>
       <c r="K54" s="11">
-        <v>5.4347149499E-3</v>
+        <v>5.4356364930999998E-3</v>
       </c>
       <c r="L54" s="19">
         <v>44.854999999999997</v>
@@ -21390,7 +21316,7 @@
         <v>12</v>
       </c>
       <c r="K55" s="11">
-        <v>1.1195158618E-2</v>
+        <v>1.1195449203E-2</v>
       </c>
       <c r="L55" s="19">
         <v>50.978000000000002</v>
@@ -21406,7 +21332,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="11">
-        <v>1.228642647E-2</v>
+        <v>1.2283056803E-2</v>
       </c>
       <c r="L56" s="19">
         <v>66.174999999999997</v>
@@ -21422,7 +21348,7 @@
         <v>14</v>
       </c>
       <c r="K57" s="11">
-        <v>6.2000507035999998E-3</v>
+        <v>6.1976211626999997E-3</v>
       </c>
       <c r="L57" s="19">
         <v>96.876000000000005</v>
@@ -21438,7 +21364,7 @@
         <v>15</v>
       </c>
       <c r="K58" s="11">
-        <v>2.3265774455E-3</v>
+        <v>2.3260121433999999E-3</v>
       </c>
       <c r="L58" s="19">
         <v>149.39099999999999</v>
@@ -21455,42 +21381,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="53" t="s">
+      <c r="A60" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="53"/>
-      <c r="C60" s="53"/>
-      <c r="D60" s="53"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="53"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="53"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="53"/>
-      <c r="L60" s="53"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
     </row>
     <row r="61" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="53" t="s">
+      <c r="A61" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="53"/>
-      <c r="C61" s="53"/>
-      <c r="D61" s="53" t="s">
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53" t="s">
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="53"/>
-      <c r="I61" s="53"/>
-      <c r="J61" s="53" t="s">
+      <c r="H61" s="46"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="53"/>
-      <c r="L61" s="53"/>
+      <c r="K61" s="46"/>
+      <c r="L61" s="46"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -21534,8 +21460,8 @@
       <c r="A63" s="19">
         <v>1</v>
       </c>
-      <c r="B63" s="69">
-        <v>0.10562470228</v>
+      <c r="B63" s="45">
+        <v>0.10600472226</v>
       </c>
       <c r="C63" s="19">
         <v>20</v>
@@ -21544,7 +21470,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="11">
-        <v>3.5687432260999999E-3</v>
+        <v>3.5906399169999999E-3</v>
       </c>
       <c r="F63" s="20">
         <v>7.3890000000000002</v>
@@ -21553,7 +21479,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="11">
-        <v>6.8195894787000002E-4</v>
+        <v>6.8494189307000001E-4</v>
       </c>
       <c r="I63" s="22">
         <v>5.6689999999999996</v>
@@ -21562,7 +21488,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="11">
-        <v>6.8195894787000002E-4</v>
+        <v>6.8494189307000001E-4</v>
       </c>
       <c r="L63" s="19">
         <v>5.6689999999999996</v>
@@ -21573,7 +21499,7 @@
         <v>2</v>
       </c>
       <c r="E64" s="11">
-        <v>5.4621180757000003E-2</v>
+        <v>5.4754394897E-2</v>
       </c>
       <c r="F64" s="19">
         <v>17.800999999999998</v>
@@ -21582,7 +21508,7 @@
         <v>2</v>
       </c>
       <c r="H64" s="11">
-        <v>1.0365402021E-2</v>
+        <v>1.0387614044E-2</v>
       </c>
       <c r="I64" s="22">
         <v>9.7479999999999993</v>
@@ -21591,7 +21517,7 @@
         <v>2</v>
       </c>
       <c r="K64" s="11">
-        <v>6.6171555847999997E-3</v>
+        <v>6.6352169913999996E-3</v>
       </c>
       <c r="L64" s="19">
         <v>9</v>
@@ -21602,7 +21528,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="11">
-        <v>5.4725110686E-2</v>
+        <v>5.4887074041000003E-2</v>
       </c>
       <c r="F65" s="19">
         <v>47.457999999999998</v>
@@ -21611,7 +21537,7 @@
         <v>3</v>
       </c>
       <c r="H65" s="11">
-        <v>1.8770927146E-2</v>
+        <v>1.8809590221999999E-2</v>
       </c>
       <c r="I65" s="22">
         <v>16.962</v>
@@ -21620,7 +21546,7 @@
         <v>3</v>
       </c>
       <c r="K65" s="11">
-        <v>7.3240882882999996E-3</v>
+        <v>7.3335188779999998E-3</v>
       </c>
       <c r="L65" s="19">
         <v>12.718999999999999</v>
@@ -21634,7 +21560,7 @@
         <v>4</v>
       </c>
       <c r="H66" s="11">
-        <v>2.8583969422000002E-2</v>
+        <v>2.8673004932999999E-2</v>
       </c>
       <c r="I66" s="22">
         <v>26.009</v>
@@ -21643,7 +21569,7 @@
         <v>4</v>
       </c>
       <c r="K66" s="11">
-        <v>9.9610281605000007E-3</v>
+        <v>9.9815484057999993E-3</v>
       </c>
       <c r="L66" s="19">
         <v>16.966000000000001</v>
@@ -21656,7 +21582,7 @@
         <v>5</v>
       </c>
       <c r="H67" s="11">
-        <v>3.4909624267999997E-2</v>
+        <v>3.5024138980000001E-2</v>
       </c>
       <c r="I67" s="22">
         <v>41.75</v>
@@ -21665,7 +21591,7 @@
         <v>5</v>
       </c>
       <c r="K67" s="11">
-        <v>1.0385777621E-2</v>
+        <v>1.0419421319E-2</v>
       </c>
       <c r="L67" s="19">
         <v>20.881</v>
@@ -21678,7 +21604,7 @@
         <v>6</v>
       </c>
       <c r="H68" s="11">
-        <v>1.8649321238000002E-2</v>
+        <v>1.8693392589000001E-2</v>
       </c>
       <c r="I68" s="22">
         <v>72.683000000000007</v>
@@ -21687,7 +21613,7 @@
         <v>6</v>
       </c>
       <c r="K68" s="11">
-        <v>1.0633194435E-2</v>
+        <v>1.067267916E-2</v>
       </c>
       <c r="L68" s="19">
         <v>24.969000000000001</v>
@@ -21700,7 +21626,7 @@
         <v>7</v>
       </c>
       <c r="H69" s="11">
-        <v>2.3247011072999998E-3</v>
+        <v>2.3271592403999999E-3</v>
       </c>
       <c r="I69" s="22">
         <v>149.39099999999999</v>
@@ -21709,7 +21635,7 @@
         <v>7</v>
       </c>
       <c r="K69" s="11">
-        <v>9.0715444739999998E-3</v>
+        <v>9.1047857501000001E-3</v>
       </c>
       <c r="L69" s="19">
         <v>28.847999999999999</v>
@@ -21725,7 +21651,7 @@
         <v>8</v>
       </c>
       <c r="K70" s="11">
-        <v>8.0924185103000007E-3</v>
+        <v>8.1182610155000005E-3</v>
       </c>
       <c r="L70" s="19">
         <v>33.03</v>
@@ -21741,7 +21667,7 @@
         <v>9</v>
       </c>
       <c r="K71" s="11">
-        <v>7.1390395186000004E-3</v>
+        <v>7.1640315452000001E-3</v>
       </c>
       <c r="L71" s="19">
         <v>36.945</v>
@@ -21757,7 +21683,7 @@
         <v>10</v>
       </c>
       <c r="K72" s="11">
-        <v>7.0519320200000003E-3</v>
+        <v>7.0755841980000003E-3</v>
       </c>
       <c r="L72" s="19">
         <v>40.929000000000002</v>
@@ -21773,7 +21699,7 @@
         <v>11</v>
       </c>
       <c r="K73" s="11">
-        <v>5.4269814703000003E-3</v>
+        <v>5.4428889523999999E-3</v>
       </c>
       <c r="L73" s="19">
         <v>44.854999999999997</v>
@@ -21789,7 +21715,7 @@
         <v>12</v>
       </c>
       <c r="K74" s="11">
-        <v>1.1177337842E-2</v>
+        <v>1.1210108196000001E-2</v>
       </c>
       <c r="L74" s="19">
         <v>50.978000000000002</v>
@@ -21805,7 +21731,7 @@
         <v>13</v>
       </c>
       <c r="K75" s="11">
-        <v>1.2268752492000001E-2</v>
+        <v>1.2300530694E-2</v>
       </c>
       <c r="L75" s="19">
         <v>66.174999999999997</v>
@@ -21821,7 +21747,7 @@
         <v>14</v>
       </c>
       <c r="K76" s="11">
-        <v>6.1926200578000003E-3</v>
+        <v>6.2035869655999998E-3</v>
       </c>
       <c r="L76" s="19">
         <v>96.876000000000005</v>
@@ -21837,7 +21763,7 @@
         <v>15</v>
       </c>
       <c r="K77" s="11">
-        <v>2.3247011072999998E-3</v>
+        <v>2.3271592403999999E-3</v>
       </c>
       <c r="L77" s="19">
         <v>149.39099999999999</v>
@@ -21905,61 +21831,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="59"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="55"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54" t="s">
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="54" t="s">
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="55"/>
-      <c r="M3" s="56"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -22004,82 +21930,82 @@
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="69">
-        <v>0.10667341828</v>
-      </c>
-      <c r="C5" s="69">
-        <v>3.4489036102999998E-2</v>
-      </c>
-      <c r="D5" s="69">
-        <v>2.0725297343E-2</v>
-      </c>
-      <c r="E5" s="69">
-        <v>0.11391673011</v>
-      </c>
-      <c r="F5" s="69">
-        <v>3.5675554983999998E-2</v>
-      </c>
-      <c r="G5" s="69">
-        <v>2.0915480577999999E-2</v>
-      </c>
-      <c r="H5" s="69">
-        <v>0.11536486167</v>
-      </c>
-      <c r="I5" s="69">
-        <v>3.5778101541000001E-2</v>
-      </c>
-      <c r="J5" s="69">
-        <v>2.114158608E-2</v>
-      </c>
-      <c r="K5" s="69">
-        <v>0.11538709508</v>
-      </c>
-      <c r="L5" s="69">
-        <v>3.5775580645999998E-2</v>
-      </c>
-      <c r="M5" s="69">
-        <v>2.1159004222999999E-2</v>
+      <c r="B5" s="45">
+        <v>0.10591209522</v>
+      </c>
+      <c r="C5" s="45">
+        <v>9.8261392613000001E-2</v>
+      </c>
+      <c r="D5" s="45">
+        <v>6.8156319210000002E-3</v>
+      </c>
+      <c r="E5" s="45">
+        <v>0.11307317075999999</v>
+      </c>
+      <c r="F5" s="45">
+        <v>0.10151440522000001</v>
+      </c>
+      <c r="G5" s="45">
+        <v>6.5754860800999997E-3</v>
+      </c>
+      <c r="H5" s="45">
+        <v>0.11449726077</v>
+      </c>
+      <c r="I5" s="45">
+        <v>0.10204099488</v>
+      </c>
+      <c r="J5" s="45">
+        <v>6.2446316854000003E-3</v>
+      </c>
+      <c r="K5" s="45">
+        <v>0.11451569712</v>
+      </c>
+      <c r="L5" s="45">
+        <v>0.10187985982</v>
+      </c>
+      <c r="M5" s="45">
+        <v>6.2446316854000003E-3</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="52"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="54" t="s">
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="54" t="s">
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="49"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -22124,82 +22050,82 @@
       <c r="A9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="69">
-        <v>0.1065761207</v>
-      </c>
-      <c r="C9" s="69">
-        <v>3.4544142375000003E-2</v>
-      </c>
-      <c r="D9" s="69">
-        <v>2.063395673E-2</v>
-      </c>
-      <c r="E9" s="69">
-        <v>0.11390416292</v>
-      </c>
-      <c r="F9" s="69">
-        <v>3.5733566759000003E-2</v>
-      </c>
-      <c r="G9" s="69">
-        <v>2.0891407612E-2</v>
-      </c>
-      <c r="H9" s="69">
-        <v>0.11538074608</v>
-      </c>
-      <c r="I9" s="69">
-        <v>3.5998224927999999E-2</v>
-      </c>
-      <c r="J9" s="69">
-        <v>2.0923201988999999E-2</v>
-      </c>
-      <c r="K9" s="69">
-        <v>0.11539380782</v>
-      </c>
-      <c r="L9" s="69">
-        <v>3.5982564204999998E-2</v>
-      </c>
-      <c r="M9" s="69">
-        <v>2.0942802930999999E-2</v>
+      <c r="B9" s="45">
+        <v>0.10582604926</v>
+      </c>
+      <c r="C9" s="45">
+        <v>9.8287056654999996E-2</v>
+      </c>
+      <c r="D9" s="45">
+        <v>6.7255702446000001E-3</v>
+      </c>
+      <c r="E9" s="45">
+        <v>0.11307004577</v>
+      </c>
+      <c r="F9" s="45">
+        <v>0.10154732862</v>
+      </c>
+      <c r="G9" s="45">
+        <v>6.4066530529000004E-3</v>
+      </c>
+      <c r="H9" s="45">
+        <v>0.11451740733</v>
+      </c>
+      <c r="I9" s="45">
+        <v>0.10208158338999999</v>
+      </c>
+      <c r="J9" s="45">
+        <v>6.4066530529000004E-3</v>
+      </c>
+      <c r="K9" s="45">
+        <v>0.11452593874</v>
+      </c>
+      <c r="L9" s="45">
+        <v>0.10191392534</v>
+      </c>
+      <c r="M9" s="45">
+        <v>6.4066530529000004E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="54" t="s">
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="55"/>
-      <c r="M11" s="56"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="49"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -22244,82 +22170,82 @@
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="69">
-        <v>0.10674620687</v>
-      </c>
-      <c r="C13" s="69">
-        <v>3.5062014427999999E-2</v>
-      </c>
-      <c r="D13" s="69">
-        <v>2.0826266635999999E-2</v>
-      </c>
-      <c r="E13" s="69">
-        <v>0.11385843209</v>
-      </c>
-      <c r="F13" s="69">
-        <v>3.6014315565000003E-2</v>
-      </c>
-      <c r="G13" s="69">
-        <v>2.1200341402999999E-2</v>
-      </c>
-      <c r="H13" s="69">
-        <v>0.11527295948999999</v>
-      </c>
-      <c r="I13" s="69">
-        <v>3.6280286283E-2</v>
-      </c>
-      <c r="J13" s="69">
-        <v>2.1218906289999999E-2</v>
-      </c>
-      <c r="K13" s="69">
-        <v>0.11534586400999999</v>
-      </c>
-      <c r="L13" s="69">
-        <v>3.6327894915999998E-2</v>
-      </c>
-      <c r="M13" s="69">
-        <v>2.1223086402000001E-2</v>
+      <c r="B13" s="45">
+        <v>0.10598658074</v>
+      </c>
+      <c r="C13" s="45">
+        <v>9.8436287063999997E-2</v>
+      </c>
+      <c r="D13" s="45">
+        <v>6.8993340752999998E-3</v>
+      </c>
+      <c r="E13" s="45">
+        <v>0.11302241352</v>
+      </c>
+      <c r="F13" s="45">
+        <v>0.10162040609</v>
+      </c>
+      <c r="G13" s="45">
+        <v>6.0217485433999999E-3</v>
+      </c>
+      <c r="H13" s="45">
+        <v>0.11441054891999999</v>
+      </c>
+      <c r="I13" s="45">
+        <v>0.10209473717000001</v>
+      </c>
+      <c r="J13" s="45">
+        <v>6.0217485433999999E-3</v>
+      </c>
+      <c r="K13" s="45">
+        <v>0.11447921302</v>
+      </c>
+      <c r="L13" s="45">
+        <v>0.1019806061</v>
+      </c>
+      <c r="M13" s="45">
+        <v>6.0217485433999999E-3</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54" t="s">
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="54" t="s">
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="55"/>
-      <c r="M15" s="56"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -22364,41 +22290,41 @@
       <c r="A17" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="69">
-        <v>0.10657675044000001</v>
-      </c>
-      <c r="C17" s="69">
-        <v>3.5689816924999999E-2</v>
-      </c>
-      <c r="D17" s="69">
-        <v>2.0974047853999998E-2</v>
-      </c>
-      <c r="E17" s="69">
-        <v>0.11392468854</v>
-      </c>
-      <c r="F17" s="69">
-        <v>3.6719551507000001E-2</v>
-      </c>
-      <c r="G17" s="69">
-        <v>2.1458496861000001E-2</v>
-      </c>
-      <c r="H17" s="69">
-        <v>0.11531296486000001</v>
-      </c>
-      <c r="I17" s="69">
-        <v>3.6905445399000002E-2</v>
-      </c>
-      <c r="J17" s="69">
-        <v>2.1470311076E-2</v>
-      </c>
-      <c r="K17" s="69">
-        <v>0.11540415636</v>
-      </c>
-      <c r="L17" s="69">
-        <v>3.6945089569E-2</v>
-      </c>
-      <c r="M17" s="69">
-        <v>2.1470360441000001E-2</v>
+      <c r="B17" s="45">
+        <v>0.10580586314</v>
+      </c>
+      <c r="C17" s="45">
+        <v>9.8429453846000006E-2</v>
+      </c>
+      <c r="D17" s="45">
+        <v>6.4072851163000004E-3</v>
+      </c>
+      <c r="E17" s="45">
+        <v>0.11307862356999999</v>
+      </c>
+      <c r="F17" s="45">
+        <v>0.10175280512</v>
+      </c>
+      <c r="G17" s="45">
+        <v>6.0910721046E-3</v>
+      </c>
+      <c r="H17" s="45">
+        <v>0.11445107802</v>
+      </c>
+      <c r="I17" s="45">
+        <v>0.10220731084</v>
+      </c>
+      <c r="J17" s="45">
+        <v>6.0910721046E-3</v>
+      </c>
+      <c r="K17" s="45">
+        <v>0.11453533261</v>
+      </c>
+      <c r="L17" s="45">
+        <v>0.10212470317</v>
+      </c>
+      <c r="M17" s="45">
+        <v>6.0910721046E-3</v>
       </c>
     </row>
   </sheetData>
@@ -22449,74 +22375,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -22560,8 +22486,8 @@
       <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="69">
-        <v>0.10667341828</v>
+      <c r="B6" s="45">
+        <v>0.10591209522</v>
       </c>
       <c r="C6" s="19">
         <v>20</v>
@@ -22570,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="11">
-        <v>3.6146051232E-3</v>
+        <v>3.5971340051999998E-3</v>
       </c>
       <c r="F6" s="20">
         <v>7.3890000000000002</v>
@@ -22579,7 +22505,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="11">
-        <v>6.9675725407999998E-4</v>
+        <v>6.9454809358E-4</v>
       </c>
       <c r="I6" s="22">
         <v>5.6689999999999996</v>
@@ -22588,7 +22514,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="11">
-        <v>6.9675725407999998E-4</v>
+        <v>6.9454809358E-4</v>
       </c>
       <c r="L6" s="19">
         <v>5.6689999999999996</v>
@@ -22602,7 +22528,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="11">
-        <v>5.5054108470000002E-2</v>
+        <v>5.4673820142999999E-2</v>
       </c>
       <c r="F7" s="19">
         <v>17.800999999999998</v>
@@ -22611,7 +22537,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="11">
-        <v>1.0466067857E-2</v>
+        <v>1.0405734058999999E-2</v>
       </c>
       <c r="I7" s="22">
         <v>9.7479999999999993</v>
@@ -22620,7 +22546,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="11">
-        <v>6.6498645921000002E-3</v>
+        <v>6.6124737778000004E-3</v>
       </c>
       <c r="L7" s="19">
         <v>9</v>
@@ -22634,7 +22560,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="11">
-        <v>5.5248016513000001E-2</v>
+        <v>5.4802216611000001E-2</v>
       </c>
       <c r="F8" s="19">
         <v>47.457999999999998</v>
@@ -22643,7 +22569,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="11">
-        <v>1.8927980431999999E-2</v>
+        <v>1.8796281737000001E-2</v>
       </c>
       <c r="I8" s="22">
         <v>16.962</v>
@@ -22652,7 +22578,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="11">
-        <v>7.3828482207E-3</v>
+        <v>7.3343176586999998E-3</v>
       </c>
       <c r="L8" s="19">
         <v>12.718999999999999</v>
@@ -22669,7 +22595,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="11">
-        <v>2.8855919224999999E-2</v>
+        <v>2.8641219329999999E-2</v>
       </c>
       <c r="I9" s="22">
         <v>26.009</v>
@@ -22678,7 +22604,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="11">
-        <v>1.0044335595E-2</v>
+        <v>9.9744358575999999E-3</v>
       </c>
       <c r="L9" s="19">
         <v>16.966000000000001</v>
@@ -22695,7 +22621,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="11">
-        <v>3.5240597185E-2</v>
+        <v>3.4960749779000003E-2</v>
       </c>
       <c r="I10" s="22">
         <v>41.75</v>
@@ -22704,7 +22630,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="11">
-        <v>1.0482633682E-2</v>
+        <v>1.0406646780000001E-2</v>
       </c>
       <c r="L10" s="19">
         <v>20.881</v>
@@ -22721,7 +22647,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="11">
-        <v>1.8830831656E-2</v>
+        <v>1.8672559605E-2</v>
       </c>
       <c r="I11" s="22">
         <v>72.683000000000007</v>
@@ -22730,7 +22656,7 @@
         <v>6</v>
       </c>
       <c r="K11" s="11">
-        <v>1.0730067189999999E-2</v>
+        <v>1.0650613476E-2</v>
       </c>
       <c r="L11" s="19">
         <v>24.969000000000001</v>
@@ -22747,7 +22673,7 @@
         <v>7</v>
       </c>
       <c r="H12" s="11">
-        <v>2.3467080590999999E-3</v>
+        <v>2.3261681631999999E-3</v>
       </c>
       <c r="I12" s="22">
         <v>149.39099999999999</v>
@@ -22756,7 +22682,7 @@
         <v>7</v>
       </c>
       <c r="K12" s="11">
-        <v>9.1522378226000008E-3</v>
+        <v>9.0825162614999993E-3</v>
       </c>
       <c r="L12" s="19">
         <v>28.847999999999999</v>
@@ -22776,7 +22702,7 @@
         <v>8</v>
       </c>
       <c r="K13" s="11">
-        <v>8.1645451009000006E-3</v>
+        <v>8.1014486619000008E-3</v>
       </c>
       <c r="L13" s="19">
         <v>33.03</v>
@@ -22796,7 +22722,7 @@
         <v>9</v>
       </c>
       <c r="K14" s="11">
-        <v>7.2089024481000004E-3</v>
+        <v>7.1525130214999998E-3</v>
       </c>
       <c r="L14" s="19">
         <v>36.945</v>
@@ -22816,7 +22742,7 @@
         <v>10</v>
       </c>
       <c r="K15" s="11">
-        <v>7.1179707750000003E-3</v>
+        <v>7.0617375961000003E-3</v>
       </c>
       <c r="L15" s="19">
         <v>40.929000000000002</v>
@@ -22836,7 +22762,7 @@
         <v>11</v>
       </c>
       <c r="K16" s="11">
-        <v>5.4794361259000003E-3</v>
+        <v>5.4354195379000001E-3</v>
       </c>
       <c r="L16" s="19">
         <v>44.854999999999997</v>
@@ -22856,7 +22782,7 @@
         <v>12</v>
       </c>
       <c r="K17" s="11">
-        <v>1.1287683337000001E-2</v>
+        <v>1.1196744660000001E-2</v>
       </c>
       <c r="L17" s="19">
         <v>50.978000000000002</v>
@@ -22876,7 +22802,7 @@
         <v>13</v>
       </c>
       <c r="K18" s="11">
-        <v>1.2389637780999999E-2</v>
+        <v>1.2286280215999999E-2</v>
       </c>
       <c r="L18" s="19">
         <v>66.174999999999997</v>
@@ -22896,7 +22822,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="11">
-        <v>6.2534670953999999E-3</v>
+        <v>6.1998333631999997E-3</v>
       </c>
       <c r="L19" s="19">
         <v>96.876000000000005</v>
@@ -22916,7 +22842,7 @@
         <v>15</v>
       </c>
       <c r="K20" s="11">
-        <v>2.3467080590999999E-3</v>
+        <v>2.3261681631999999E-3</v>
       </c>
       <c r="L20" s="19">
         <v>149.39099999999999</v>
@@ -22937,42 +22863,42 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="66"/>
-      <c r="L22" s="66"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
     </row>
     <row r="23" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53" t="s">
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53" t="s">
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
@@ -23016,8 +22942,8 @@
       <c r="A25" s="19">
         <v>1</v>
       </c>
-      <c r="B25" s="69">
-        <v>0.1065761207</v>
+      <c r="B25" s="45">
+        <v>0.10582604926</v>
       </c>
       <c r="C25" s="19">
         <v>20</v>
@@ -23026,7 +22952,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="11">
-        <v>3.6169827736E-3</v>
+        <v>3.5990052071000001E-3</v>
       </c>
       <c r="F25" s="20">
         <v>7.3890000000000002</v>
@@ -23035,7 +22961,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="11">
-        <v>6.9938045105999999E-4</v>
+        <v>6.9731158176000003E-4</v>
       </c>
       <c r="I25" s="22">
         <v>5.6689999999999996</v>
@@ -23044,7 +22970,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="11">
-        <v>6.9938045105999999E-4</v>
+        <v>6.9731158176000003E-4</v>
       </c>
       <c r="L25" s="19">
         <v>5.6689999999999996</v>
@@ -23058,7 +22984,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="11">
-        <v>5.5012453292000003E-2</v>
+        <v>5.4638897557999999E-2</v>
       </c>
       <c r="F26" s="19">
         <v>17.800999999999998</v>
@@ -23067,7 +22993,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="11">
-        <v>1.0461591770999999E-2</v>
+        <v>1.0400648089E-2</v>
       </c>
       <c r="I26" s="22">
         <v>9.7479999999999993</v>
@@ -23076,7 +23002,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="11">
-        <v>6.6322723548999998E-3</v>
+        <v>6.5937296549000001E-3</v>
       </c>
       <c r="L26" s="19">
         <v>9</v>
@@ -23090,7 +23016,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="11">
-        <v>5.5274726854999998E-2</v>
+        <v>5.4832143000999999E-2</v>
       </c>
       <c r="F27" s="19">
         <v>47.457999999999998</v>
@@ -23099,7 +23025,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="11">
-        <v>1.8921122605999999E-2</v>
+        <v>1.8791069638999999E-2</v>
       </c>
       <c r="I27" s="22">
         <v>16.962</v>
@@ -23108,7 +23034,7 @@
         <v>3</v>
       </c>
       <c r="K27" s="11">
-        <v>7.3818369928000003E-3</v>
+        <v>7.3341238068999996E-3</v>
       </c>
       <c r="L27" s="19">
         <v>12.718999999999999</v>
@@ -23125,7 +23051,7 @@
         <v>4</v>
       </c>
       <c r="H28" s="11">
-        <v>2.88622441E-2</v>
+        <v>2.8649701068000001E-2</v>
       </c>
       <c r="I28" s="22">
         <v>26.009</v>
@@ -23134,7 +23060,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="11">
-        <v>1.004073242E-2</v>
+        <v>9.9717039944999999E-3</v>
       </c>
       <c r="L28" s="19">
         <v>16.966000000000001</v>
@@ -23151,7 +23077,7 @@
         <v>5</v>
       </c>
       <c r="H29" s="11">
-        <v>3.5255485016000003E-2</v>
+        <v>3.4976575489000003E-2</v>
       </c>
       <c r="I29" s="22">
         <v>41.75</v>
@@ -23160,7 +23086,7 @@
         <v>5</v>
       </c>
       <c r="K29" s="11">
-        <v>1.0483389244E-2</v>
+        <v>1.0408792003E-2</v>
       </c>
       <c r="L29" s="19">
         <v>20.881</v>
@@ -23177,7 +23103,7 @@
         <v>6</v>
       </c>
       <c r="H30" s="11">
-        <v>1.8833780205000001E-2</v>
+        <v>1.8675534596999999E-2</v>
       </c>
       <c r="I30" s="22">
         <v>72.683000000000007</v>
@@ -23186,7 +23112,7 @@
         <v>6</v>
       </c>
       <c r="K30" s="11">
-        <v>1.0731097130000001E-2</v>
+        <v>1.0651820540999999E-2</v>
       </c>
       <c r="L30" s="19">
         <v>24.969000000000001</v>
@@ -23203,7 +23129,7 @@
         <v>7</v>
       </c>
       <c r="H31" s="11">
-        <v>2.3471419341000001E-3</v>
+        <v>2.3265668710999998E-3</v>
       </c>
       <c r="I31" s="22">
         <v>149.39099999999999</v>
@@ -23212,7 +23138,7 @@
         <v>7</v>
       </c>
       <c r="K31" s="11">
-        <v>9.1564254636999996E-3</v>
+        <v>9.0876996899999993E-3</v>
       </c>
       <c r="L31" s="19">
         <v>28.847999999999999</v>
@@ -23232,7 +23158,7 @@
         <v>8</v>
       </c>
       <c r="K32" s="11">
-        <v>8.1686902081000001E-3</v>
+        <v>8.1056302487000007E-3</v>
       </c>
       <c r="L32" s="19">
         <v>33.03</v>
@@ -23252,7 +23178,7 @@
         <v>9</v>
       </c>
       <c r="K33" s="11">
-        <v>7.2106240137999999E-3</v>
+        <v>7.1546067802000001E-3</v>
       </c>
       <c r="L33" s="19">
         <v>36.945</v>
@@ -23272,7 +23198,7 @@
         <v>10</v>
       </c>
       <c r="K34" s="11">
-        <v>7.1209308174000003E-3</v>
+        <v>7.0646717281000002E-3</v>
       </c>
       <c r="L34" s="19">
         <v>40.929000000000002</v>
@@ -23292,7 +23218,7 @@
         <v>11</v>
       </c>
       <c r="K35" s="11">
-        <v>5.4822822109000004E-3</v>
+        <v>5.4385447326999996E-3</v>
       </c>
       <c r="L35" s="19">
         <v>44.854999999999997</v>
@@ -23312,7 +23238,7 @@
         <v>12</v>
       </c>
       <c r="K36" s="11">
-        <v>1.1293175898E-2</v>
+        <v>1.1201844230000001E-2</v>
       </c>
       <c r="L36" s="19">
         <v>50.978000000000002</v>
@@ -23332,7 +23258,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="11">
-        <v>1.2391350807999999E-2</v>
+        <v>1.2288125356000001E-2</v>
       </c>
       <c r="L37" s="19">
         <v>66.174999999999997</v>
@@ -23352,7 +23278,7 @@
         <v>14</v>
       </c>
       <c r="K38" s="11">
-        <v>6.2544778716000001E-3</v>
+        <v>6.2007675184000003E-3</v>
       </c>
       <c r="L38" s="19">
         <v>96.876000000000005</v>
@@ -23372,7 +23298,7 @@
         <v>15</v>
       </c>
       <c r="K39" s="11">
-        <v>2.3471419341000001E-3</v>
+        <v>2.3265668710999998E-3</v>
       </c>
       <c r="L39" s="19">
         <v>149.39099999999999</v>
@@ -23393,42 +23319,42 @@
       <c r="L40" s="26"/>
     </row>
     <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
     </row>
     <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53" t="s">
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53" t="s">
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="53"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53" t="s">
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -23472,8 +23398,8 @@
       <c r="A44" s="19">
         <v>1</v>
       </c>
-      <c r="B44" s="69">
-        <v>0.10674620687</v>
+      <c r="B44" s="45">
+        <v>0.10598658074</v>
       </c>
       <c r="C44" s="19">
         <v>20</v>
@@ -23482,7 +23408,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="11">
-        <v>3.6100749178999999E-3</v>
+        <v>3.5939040021000001E-3</v>
       </c>
       <c r="F44" s="20">
         <v>7.3890000000000002</v>
@@ -23491,7 +23417,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="11">
-        <v>6.9012776483000002E-4</v>
+        <v>6.8923874264999998E-4</v>
       </c>
       <c r="I44" s="22">
         <v>5.6689999999999996</v>
@@ -23500,7 +23426,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="11">
-        <v>6.9012776483000002E-4</v>
+        <v>6.8923874264999998E-4</v>
       </c>
       <c r="L44" s="19">
         <v>5.6689999999999996</v>
@@ -23514,7 +23440,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="11">
-        <v>5.5027462739999998E-2</v>
+        <v>5.4651955630999997E-2</v>
       </c>
       <c r="F45" s="19">
         <v>17.800999999999998</v>
@@ -23523,7 +23449,7 @@
         <v>2</v>
       </c>
       <c r="H45" s="11">
-        <v>1.0405672656E-2</v>
+        <v>1.0347427641999999E-2</v>
       </c>
       <c r="I45" s="22">
         <v>9.7479999999999993</v>
@@ -23532,7 +23458,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="11">
-        <v>6.6367972943999999E-3</v>
+        <v>6.6008099792999996E-3</v>
       </c>
       <c r="L45" s="19">
         <v>9</v>
@@ -23546,7 +23472,7 @@
         <v>3</v>
       </c>
       <c r="E46" s="11">
-        <v>5.5220894435000001E-2</v>
+        <v>5.4776553891000002E-2</v>
       </c>
       <c r="F46" s="19">
         <v>47.457999999999998</v>
@@ -23555,7 +23481,7 @@
         <v>3</v>
       </c>
       <c r="H46" s="11">
-        <v>1.8942681116000001E-2</v>
+        <v>1.8810617583999999E-2</v>
       </c>
       <c r="I46" s="22">
         <v>16.962</v>
@@ -23564,7 +23490,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="11">
-        <v>7.3808931271000001E-3</v>
+        <v>7.3344773036999999E-3</v>
       </c>
       <c r="L46" s="19">
         <v>12.718999999999999</v>
@@ -23581,7 +23507,7 @@
         <v>4</v>
       </c>
       <c r="H47" s="11">
-        <v>2.8837890307E-2</v>
+        <v>2.8624237893000001E-2</v>
       </c>
       <c r="I47" s="22">
         <v>26.009</v>
@@ -23590,7 +23516,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11">
-        <v>1.005209967E-2</v>
+        <v>9.9820038885000007E-3</v>
       </c>
       <c r="L47" s="19">
         <v>16.966000000000001</v>
@@ -23607,7 +23533,7 @@
         <v>5</v>
       </c>
       <c r="H48" s="11">
-        <v>3.5224531189999998E-2</v>
+        <v>3.4946007251E-2</v>
       </c>
       <c r="I48" s="22">
         <v>41.75</v>
@@ -23616,7 +23542,7 @@
         <v>5</v>
       </c>
       <c r="K48" s="11">
-        <v>1.0485678642E-2</v>
+        <v>1.0409672583000001E-2</v>
       </c>
       <c r="L48" s="19">
         <v>20.881</v>
@@ -23633,7 +23559,7 @@
         <v>6</v>
       </c>
       <c r="H49" s="11">
-        <v>1.8825170624E-2</v>
+        <v>1.8666682859999999E-2</v>
       </c>
       <c r="I49" s="22">
         <v>72.683000000000007</v>
@@ -23642,7 +23568,7 @@
         <v>6</v>
       </c>
       <c r="K49" s="11">
-        <v>1.0727592459000001E-2</v>
+        <v>1.0647669424E-2</v>
       </c>
       <c r="L49" s="19">
         <v>24.969000000000001</v>
@@ -23659,7 +23585,7 @@
         <v>7</v>
       </c>
       <c r="H50" s="11">
-        <v>2.3468858287000001E-3</v>
+        <v>2.3263369440000002E-3</v>
       </c>
       <c r="I50" s="22">
         <v>149.39099999999999</v>
@@ -23668,7 +23594,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="11">
-        <v>9.1471146380999995E-3</v>
+        <v>9.0777829554999998E-3</v>
       </c>
       <c r="L50" s="19">
         <v>28.847999999999999</v>
@@ -23688,7 +23614,7 @@
         <v>8</v>
       </c>
       <c r="K51" s="11">
-        <v>8.1604039999999996E-3</v>
+        <v>8.0974959250999998E-3</v>
       </c>
       <c r="L51" s="19">
         <v>33.03</v>
@@ -23708,7 +23634,7 @@
         <v>9</v>
       </c>
       <c r="K52" s="11">
-        <v>7.205254316E-3</v>
+        <v>7.1490887458000004E-3</v>
       </c>
       <c r="L52" s="19">
         <v>36.945</v>
@@ -23728,7 +23654,7 @@
         <v>10</v>
       </c>
       <c r="K53" s="11">
-        <v>7.1145990055999997E-3</v>
+        <v>7.0584367312000003E-3</v>
       </c>
       <c r="L53" s="19">
         <v>40.929000000000002</v>
@@ -23748,7 +23674,7 @@
         <v>11</v>
       </c>
       <c r="K54" s="11">
-        <v>5.4770564905000001E-3</v>
+        <v>5.4334551476000002E-3</v>
       </c>
       <c r="L54" s="19">
         <v>44.854999999999997</v>
@@ -23768,7 +23694,7 @@
         <v>12</v>
       </c>
       <c r="K55" s="11">
-        <v>1.1283648197E-2</v>
+        <v>1.1192234295000001E-2</v>
       </c>
       <c r="L55" s="19">
         <v>50.978000000000002</v>
@@ -23788,7 +23714,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="11">
-        <v>1.2385500303000001E-2</v>
+        <v>1.2282049583999999E-2</v>
       </c>
       <c r="L56" s="19">
         <v>66.174999999999997</v>
@@ -23808,7 +23734,7 @@
         <v>14</v>
       </c>
       <c r="K57" s="11">
-        <v>6.2522122692E-3</v>
+        <v>6.1984607738999999E-3</v>
       </c>
       <c r="L57" s="19">
         <v>96.876000000000005</v>
@@ -23828,7 +23754,7 @@
         <v>15</v>
       </c>
       <c r="K58" s="11">
-        <v>2.3468858287000001E-3</v>
+        <v>2.3263369440000002E-3</v>
       </c>
       <c r="L58" s="19">
         <v>149.39099999999999</v>
@@ -23849,42 +23775,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="53" t="s">
+      <c r="A60" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="53"/>
-      <c r="C60" s="53"/>
-      <c r="D60" s="53"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="53"/>
-      <c r="G60" s="53"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="53"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="53"/>
-      <c r="L60" s="53"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
     </row>
     <row r="61" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="53" t="s">
+      <c r="A61" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="53"/>
-      <c r="C61" s="53"/>
-      <c r="D61" s="53" t="s">
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="53"/>
-      <c r="F61" s="53"/>
-      <c r="G61" s="53" t="s">
+      <c r="E61" s="46"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="53"/>
-      <c r="I61" s="53"/>
-      <c r="J61" s="53" t="s">
+      <c r="H61" s="46"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="53"/>
-      <c r="L61" s="53"/>
+      <c r="K61" s="46"/>
+      <c r="L61" s="46"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -23928,8 +23854,8 @@
       <c r="A63" s="19">
         <v>1</v>
       </c>
-      <c r="B63" s="69">
-        <v>0.10657675044000001</v>
+      <c r="B63" s="45">
+        <v>0.10580586314</v>
       </c>
       <c r="C63" s="19">
         <v>20</v>
@@ -23938,7 +23864,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="11">
-        <v>3.5856309420999998E-3</v>
+        <v>3.5685763996000002E-3</v>
       </c>
       <c r="F63" s="20">
         <v>7.3890000000000002</v>
@@ -23947,7 +23873,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="11">
-        <v>6.8096554518999998E-4</v>
+        <v>6.7864448784000001E-4</v>
       </c>
       <c r="I63" s="22">
         <v>5.6689999999999996</v>
@@ -23956,7 +23882,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="11">
-        <v>6.8096554518999998E-4</v>
+        <v>6.7864448784000001E-4</v>
       </c>
       <c r="L63" s="19">
         <v>5.6689999999999996</v>
@@ -23970,7 +23896,7 @@
         <v>2</v>
       </c>
       <c r="E64" s="11">
-        <v>5.5024964168999997E-2</v>
+        <v>5.4642234428000001E-2</v>
       </c>
       <c r="F64" s="19">
         <v>17.800999999999998</v>
@@ -23979,7 +23905,7 @@
         <v>2</v>
       </c>
       <c r="H64" s="11">
-        <v>1.0398856289000001E-2</v>
+        <v>1.0341006998E-2</v>
       </c>
       <c r="I64" s="22">
         <v>9.7479999999999993</v>
@@ -23988,7 +23914,7 @@
         <v>2</v>
       </c>
       <c r="K64" s="11">
-        <v>6.6459709949000002E-3</v>
+        <v>6.6066791149E-3</v>
       </c>
       <c r="L64" s="19">
         <v>9</v>
@@ -24002,7 +23928,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="11">
-        <v>5.5314093425000002E-2</v>
+        <v>5.4867812742999997E-2</v>
       </c>
       <c r="F65" s="19">
         <v>47.457999999999998</v>
@@ -24011,7 +23937,7 @@
         <v>3</v>
       </c>
       <c r="H65" s="11">
-        <v>1.8897488314999999E-2</v>
+        <v>1.8767903462E-2</v>
       </c>
       <c r="I65" s="22">
         <v>16.962</v>
@@ -24020,7 +23946,7 @@
         <v>3</v>
       </c>
       <c r="K65" s="11">
-        <v>7.3607256085999996E-3</v>
+        <v>7.3155796877000002E-3</v>
       </c>
       <c r="L65" s="19">
         <v>12.718999999999999</v>
@@ -24037,7 +23963,7 @@
         <v>4</v>
       </c>
       <c r="H66" s="11">
-        <v>2.8849507964000001E-2</v>
+        <v>2.8637430301000001E-2</v>
       </c>
       <c r="I66" s="22">
         <v>26.009</v>
@@ -24046,7 +23972,7 @@
         <v>4</v>
       </c>
       <c r="K66" s="11">
-        <v>1.0028186126E-2</v>
+        <v>9.9594066981000002E-3</v>
       </c>
       <c r="L66" s="19">
         <v>16.966000000000001</v>
@@ -24063,7 +23989,7 @@
         <v>5</v>
       </c>
       <c r="H67" s="11">
-        <v>3.5286873065000002E-2</v>
+        <v>3.5006017389999998E-2</v>
       </c>
       <c r="I67" s="22">
         <v>41.75</v>
@@ -24072,7 +23998,7 @@
         <v>5</v>
       </c>
       <c r="K67" s="11">
-        <v>1.0474833536999999E-2</v>
+        <v>1.0401472776999999E-2</v>
       </c>
       <c r="L67" s="19">
         <v>20.881</v>
@@ -24089,7 +24015,7 @@
         <v>6</v>
       </c>
       <c r="H68" s="11">
-        <v>1.8851329404E-2</v>
+        <v>1.8692573273000002E-2</v>
       </c>
       <c r="I68" s="22">
         <v>72.683000000000007</v>
@@ -24098,7 +24024,7 @@
         <v>6</v>
       </c>
       <c r="K68" s="11">
-        <v>1.0738046312E-2</v>
+        <v>1.0657706556999999E-2</v>
       </c>
       <c r="L68" s="19">
         <v>24.969000000000001</v>
@@ -24115,7 +24041,7 @@
         <v>7</v>
       </c>
       <c r="H69" s="11">
-        <v>2.3479442787999998E-3</v>
+        <v>2.3275021123999999E-3</v>
       </c>
       <c r="I69" s="22">
         <v>149.39099999999999</v>
@@ -24124,7 +24050,7 @@
         <v>7</v>
       </c>
       <c r="K69" s="11">
-        <v>9.1634821623000004E-3</v>
+        <v>9.0942562857000003E-3</v>
       </c>
       <c r="L69" s="19">
         <v>28.847999999999999</v>
@@ -24144,7 +24070,7 @@
         <v>8</v>
       </c>
       <c r="K70" s="11">
-        <v>8.1749687040000001E-3</v>
+        <v>8.1119079964000005E-3</v>
       </c>
       <c r="L70" s="19">
         <v>33.03</v>
@@ -24164,7 +24090,7 @@
         <v>9</v>
       </c>
       <c r="K71" s="11">
-        <v>7.2159566885E-3</v>
+        <v>7.1591769582999999E-3</v>
       </c>
       <c r="L71" s="19">
         <v>36.945</v>
@@ -24184,7 +24110,7 @@
         <v>10</v>
       </c>
       <c r="K72" s="11">
-        <v>7.1282615252000001E-3</v>
+        <v>7.0718259434999998E-3</v>
       </c>
       <c r="L72" s="19">
         <v>40.929000000000002</v>
@@ -24204,7 +24130,7 @@
         <v>11</v>
       </c>
       <c r="K73" s="11">
-        <v>5.4844390270000001E-3</v>
+        <v>5.4407616977999998E-3</v>
       </c>
       <c r="L73" s="19">
         <v>44.854999999999997</v>
@@ -24224,7 +24150,7 @@
         <v>12</v>
       </c>
       <c r="K74" s="11">
-        <v>1.1298794993000001E-2</v>
+        <v>1.1206648671E-2</v>
       </c>
       <c r="L74" s="19">
         <v>50.978000000000002</v>
@@ -24244,7 +24170,7 @@
         <v>13</v>
       </c>
       <c r="K75" s="11">
-        <v>1.2403288017000001E-2</v>
+        <v>1.2299370299999999E-2</v>
       </c>
       <c r="L75" s="19">
         <v>66.174999999999997</v>
@@ -24264,7 +24190,7 @@
         <v>14</v>
       </c>
       <c r="K76" s="11">
-        <v>6.2582928421000003E-3</v>
+        <v>6.2043933190999998E-3</v>
       </c>
       <c r="L76" s="19">
         <v>96.876000000000005</v>
@@ -24284,7 +24210,7 @@
         <v>15</v>
       </c>
       <c r="K77" s="11">
-        <v>2.3479442787999998E-3</v>
+        <v>2.3275021123999999E-3</v>
       </c>
       <c r="L77" s="19">
         <v>149.39099999999999</v>
@@ -24354,61 +24280,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="68"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="69"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="56"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="49"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54" t="s">
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="54" t="s">
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="55"/>
-      <c r="M3" s="56"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="37"/>
@@ -24491,44 +24417,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="56"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="49"/>
     </row>
     <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="54" t="s">
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="54" t="s">
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="49"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="37"/>
@@ -24611,44 +24537,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="56"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="54" t="s">
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="55"/>
-      <c r="M11" s="56"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="49"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="37"/>
@@ -24731,44 +24657,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="56"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54" t="s">
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="54" t="s">
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="55"/>
-      <c r="M15" s="56"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="37"/>

--- a/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
+++ b/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/007_POLIMO_CHAMPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2B9BAE-5850-CF4C-AB09-33DAE70A9947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21460D2B-D5E7-7141-8C0D-BE6E761E3060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -791,6 +791,30 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -803,15 +827,6 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -821,28 +836,13 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1276,23 +1276,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="56"/>
+      <c r="A2" s="48"/>
     </row>
     <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="56"/>
+      <c r="A3" s="48"/>
     </row>
     <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="48" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="56"/>
+      <c r="A5" s="48"/>
     </row>
     <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1330,12 +1330,12 @@
       </c>
     </row>
     <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="49" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="57"/>
+      <c r="A14" s="49"/>
     </row>
     <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1363,12 +1363,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="48" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="56"/>
+      <c r="A21" s="48"/>
     </row>
     <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -1424,13 +1424,13 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="48" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="56"/>
+      <c r="A33" s="48"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1493,12 +1493,12 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="48" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="56"/>
+      <c r="A45" s="48"/>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1562,12 +1562,12 @@
       <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="48" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="56"/>
+      <c r="A57" s="48"/>
       <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1685,17 +1685,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -2723,20 +2723,20 @@
       <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="31"/>
@@ -3748,26 +3748,26 @@
       <c r="AMG3" s="31"/>
     </row>
     <row r="4" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="46" t="s">
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="21"/>
@@ -5094,20 +5094,20 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="31"/>
@@ -6119,26 +6119,26 @@
       <c r="AMG22" s="31"/>
     </row>
     <row r="23" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="46" t="s">
+      <c r="B23" s="56"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46" t="s">
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
@@ -8488,26 +8488,26 @@
       <c r="AMG41" s="31"/>
     </row>
     <row r="42" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A42" s="47" t="s">
+      <c r="A42" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="48"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="46" t="s">
+      <c r="B42" s="56"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46" t="s">
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46" t="s">
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
@@ -10859,26 +10859,26 @@
       <c r="AMG60" s="31"/>
     </row>
     <row r="61" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="48"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="46" t="s">
+      <c r="B61" s="56"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46" t="s">
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46" t="s">
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
       <c r="M61" s="31"/>
       <c r="N61" s="31"/>
       <c r="O61" s="31"/>
@@ -12278,34 +12278,34 @@
       <c r="L2" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="49"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -12509,34 +12509,34 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="52"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="47" t="s">
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="49"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
@@ -12740,34 +12740,34 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="52"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="63"/>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46" t="s">
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="47" t="s">
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="48"/>
-      <c r="I26" s="49"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
@@ -12971,34 +12971,34 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="52"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A37" s="46" t="s">
+      <c r="A37" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46" t="s">
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="47" t="s">
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="48"/>
-      <c r="I37" s="49"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
@@ -13238,12 +13238,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
@@ -13265,16 +13265,16 @@
     </row>
     <row r="3" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B3" s="11">
-        <v>0.43934707094210002</v>
+        <v>0.46849361959300001</v>
       </c>
       <c r="C3" s="11">
-        <v>2.0295658491259999E-2</v>
+        <v>1.290927168187E-2</v>
       </c>
       <c r="D3" s="11">
-        <v>3.4792598586630002E-2</v>
+        <v>2.2130249579159999E-2</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -14298,12 +14298,12 @@
       <c r="AMJ3" s="10"/>
     </row>
     <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -14339,16 +14339,16 @@
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B6" s="11">
-        <v>0.44267425413369998</v>
+        <v>0.46798955527370001</v>
       </c>
       <c r="C6" s="11">
-        <v>2.0821317607760001E-2</v>
+        <v>1.358100670772E-2</v>
       </c>
       <c r="D6" s="11">
-        <v>3.5693713436710003E-2</v>
+        <v>2.328175950868E-2</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -15372,12 +15372,12 @@
       <c r="AMJ6" s="10"/>
     </row>
     <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -15413,16 +15413,16 @@
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B9" s="38">
-        <v>0.44319265006519998</v>
+        <v>0.465248328727</v>
       </c>
       <c r="C9" s="38">
-        <v>2.2684759008600001E-2</v>
+        <v>5.6574475149399998E-3</v>
       </c>
       <c r="D9" s="38">
-        <v>3.8888176411660001E-2</v>
+        <v>2.6841355741140001E-2</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -16446,12 +16446,12 @@
       <c r="AMJ9" s="10"/>
     </row>
     <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -16484,16 +16484,16 @@
     </row>
     <row r="12" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A12" s="11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B12" s="11">
-        <v>0.43253515759529998</v>
+        <v>0.46474952064940001</v>
       </c>
       <c r="C12" s="11">
-        <v>2.028938304468E-2</v>
+        <v>1.6791354190239999E-2</v>
       </c>
       <c r="D12" s="11">
-        <v>3.4784065350119998E-2</v>
+        <v>2.8787532449549999E-2</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -17526,12 +17526,12 @@
       <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -17974,12 +17974,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18027,12 +18027,12 @@
       <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
@@ -18077,12 +18077,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -18136,12 +18136,12 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="61" t="s">
+      <c r="A10" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="63"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="53"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -18204,12 +18204,12 @@
       <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -18220,12 +18220,12 @@
       <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -18682,12 +18682,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18774,12 +18774,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
@@ -18860,12 +18860,12 @@
       <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -18957,12 +18957,12 @@
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="63"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -19065,12 +19065,12 @@
       <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -19081,12 +19081,12 @@
       <c r="O26" s="10"/>
     </row>
     <row r="27" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -19553,61 +19553,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="55"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="47" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -19652,58 +19652,82 @@
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
+      <c r="B5" s="45">
+        <v>0.10610272727</v>
+      </c>
+      <c r="C5" s="45">
+        <v>9.9379307254000002E-2</v>
+      </c>
+      <c r="D5" s="45">
+        <v>3.6735622426E-3</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.11322207441</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.10301498979</v>
+      </c>
+      <c r="G5" s="11">
+        <v>3.1145777795E-3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.11463763367</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.10353209677</v>
+      </c>
+      <c r="J5" s="11">
+        <v>3.1145777795E-3</v>
+      </c>
+      <c r="K5" s="25">
+        <v>0.11465116336</v>
+      </c>
+      <c r="L5" s="25">
+        <v>0.10339948592000001</v>
+      </c>
+      <c r="M5" s="25">
+        <v>2.9585871272999999E-3</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="47" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="48"/>
-      <c r="M7" s="49"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -19786,44 +19810,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="47" t="s">
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="48"/>
-      <c r="M11" s="49"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -19906,44 +19930,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="47" t="s">
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="48"/>
-      <c r="M15" s="49"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -20107,42 +20131,42 @@
       <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
@@ -20190,28 +20214,36 @@
       <c r="A6" s="19">
         <v>1</v>
       </c>
-      <c r="B6" s="11"/>
+      <c r="B6" s="11">
+        <v>0.10610272727</v>
+      </c>
       <c r="C6" s="19">
         <v>20</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>3.6175964050999998E-3</v>
+      </c>
       <c r="F6" s="19">
         <v>7.3890000000000002</v>
       </c>
       <c r="G6" s="19">
         <v>1</v>
       </c>
-      <c r="H6" s="11"/>
+      <c r="H6" s="11">
+        <v>7.0113710207000003E-4</v>
+      </c>
       <c r="I6" s="22">
         <v>5.6689999999999996</v>
       </c>
       <c r="J6" s="19">
         <v>1</v>
       </c>
-      <c r="K6" s="11"/>
+      <c r="K6" s="11">
+        <v>7.0113710207000003E-4</v>
+      </c>
       <c r="L6" s="19">
         <v>5.6689999999999996</v>
       </c>
@@ -20224,21 +20256,27 @@
       <c r="D7" s="19">
         <v>2</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="11">
+        <v>5.4784291601999997E-2</v>
+      </c>
       <c r="F7" s="19">
         <v>17.800999999999998</v>
       </c>
       <c r="G7" s="19">
         <v>2</v>
       </c>
-      <c r="H7" s="11"/>
+      <c r="H7" s="11">
+        <v>1.0447069668999999E-2</v>
+      </c>
       <c r="I7" s="22">
         <v>9.7479999999999993</v>
       </c>
       <c r="J7" s="19">
         <v>2</v>
       </c>
-      <c r="K7" s="11"/>
+      <c r="K7" s="11">
+        <v>6.6408885163000003E-3</v>
+      </c>
       <c r="L7" s="19">
         <v>9</v>
       </c>
@@ -20251,21 +20289,27 @@
       <c r="D8" s="19">
         <v>3</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="40">
+        <v>5.4820186404E-2</v>
+      </c>
       <c r="F8" s="19">
         <v>47.457999999999998</v>
       </c>
       <c r="G8" s="19">
         <v>3</v>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="11">
+        <v>1.8835961035000001E-2</v>
+      </c>
       <c r="I8" s="22">
         <v>16.962</v>
       </c>
       <c r="J8" s="19">
         <v>3</v>
       </c>
-      <c r="K8" s="11"/>
+      <c r="K8" s="11">
+        <v>7.3533750641000001E-3</v>
+      </c>
       <c r="L8" s="19">
         <v>12.718999999999999</v>
       </c>
@@ -20281,14 +20325,18 @@
       <c r="G9" s="19">
         <v>4</v>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="11">
+        <v>2.8678547751999999E-2</v>
+      </c>
       <c r="I9" s="22">
         <v>26.009</v>
       </c>
       <c r="J9" s="19">
         <v>4</v>
       </c>
-      <c r="K9" s="11"/>
+      <c r="K9" s="11">
+        <v>9.9954849331000007E-3</v>
+      </c>
       <c r="L9" s="19">
         <v>16.966000000000001</v>
       </c>
@@ -20303,14 +20351,18 @@
       <c r="G10" s="19">
         <v>5</v>
       </c>
-      <c r="H10" s="11"/>
+      <c r="H10" s="11">
+        <v>3.4976563075000001E-2</v>
+      </c>
       <c r="I10" s="22">
         <v>41.75</v>
       </c>
       <c r="J10" s="19">
         <v>5</v>
       </c>
-      <c r="K10" s="11"/>
+      <c r="K10" s="11">
+        <v>1.0424397243999999E-2</v>
+      </c>
       <c r="L10" s="19">
         <v>20.881</v>
       </c>
@@ -20325,14 +20377,18 @@
       <c r="G11" s="19">
         <v>6</v>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="11">
+        <v>1.8672464178E-2</v>
+      </c>
       <c r="I11" s="22">
         <v>72.683000000000007</v>
       </c>
       <c r="J11" s="19">
         <v>6</v>
       </c>
-      <c r="K11" s="11"/>
+      <c r="K11" s="11">
+        <v>1.0664914443999999E-2</v>
+      </c>
       <c r="L11" s="19">
         <v>24.969000000000001</v>
       </c>
@@ -20347,14 +20403,18 @@
       <c r="G12" s="19">
         <v>7</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="11">
+        <v>2.3258908571999999E-3</v>
+      </c>
       <c r="I12" s="22">
         <v>149.39099999999999</v>
       </c>
       <c r="J12" s="19">
         <v>7</v>
       </c>
-      <c r="K12" s="11"/>
+      <c r="K12" s="11">
+        <v>9.0926035472E-3</v>
+      </c>
       <c r="L12" s="19">
         <v>28.847999999999999</v>
       </c>
@@ -20372,7 +20432,9 @@
       <c r="J13" s="19">
         <v>8</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="11">
+        <v>8.1079196530999993E-3</v>
+      </c>
       <c r="L13" s="19">
         <v>33.03</v>
       </c>
@@ -20390,7 +20452,9 @@
       <c r="J14" s="19">
         <v>9</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="11">
+        <v>7.1569731817000002E-3</v>
+      </c>
       <c r="L14" s="19">
         <v>36.945</v>
       </c>
@@ -20408,7 +20472,9 @@
       <c r="J15" s="19">
         <v>10</v>
       </c>
-      <c r="K15" s="11"/>
+      <c r="K15" s="11">
+        <v>7.0649895331999996E-3</v>
+      </c>
       <c r="L15" s="19">
         <v>40.929000000000002</v>
       </c>
@@ -20426,7 +20492,9 @@
       <c r="J16" s="19">
         <v>11</v>
       </c>
-      <c r="K16" s="11"/>
+      <c r="K16" s="11">
+        <v>5.4375167017999999E-3</v>
+      </c>
       <c r="L16" s="19">
         <v>44.854999999999997</v>
       </c>
@@ -20444,7 +20512,9 @@
       <c r="J17" s="19">
         <v>12</v>
       </c>
-      <c r="K17" s="11"/>
+      <c r="K17" s="11">
+        <v>1.1199558597E-2</v>
+      </c>
       <c r="L17" s="19">
         <v>50.978000000000002</v>
       </c>
@@ -20462,7 +20532,9 @@
       <c r="J18" s="19">
         <v>13</v>
       </c>
-      <c r="K18" s="11"/>
+      <c r="K18" s="11">
+        <v>1.2287011675000001E-2</v>
+      </c>
       <c r="L18" s="19">
         <v>66.174999999999997</v>
       </c>
@@ -20480,7 +20552,9 @@
       <c r="J19" s="19">
         <v>14</v>
       </c>
-      <c r="K19" s="11"/>
+      <c r="K19" s="11">
+        <v>6.1985023133000004E-3</v>
+      </c>
       <c r="L19" s="19">
         <v>96.876000000000005</v>
       </c>
@@ -20498,7 +20572,9 @@
       <c r="J20" s="19">
         <v>15</v>
       </c>
-      <c r="K20" s="11"/>
+      <c r="K20" s="11">
+        <v>2.3258908571999999E-3</v>
+      </c>
       <c r="L20" s="19">
         <v>149.39099999999999</v>
       </c>
@@ -20542,26 +20618,26 @@
       <c r="Q22" s="29"/>
     </row>
     <row r="23" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46" t="s">
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46" t="s">
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
@@ -20998,26 +21074,26 @@
       <c r="Q41" s="29"/>
     </row>
     <row r="42" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="46" t="s">
+      <c r="A42" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46" t="s">
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46" t="s">
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46" t="s">
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -21381,42 +21457,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="46"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="46"/>
-      <c r="C61" s="46"/>
-      <c r="D61" s="46" t="s">
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46" t="s">
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46" t="s">
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -21831,61 +21907,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="55"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="47" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -21968,44 +22044,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="47" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="48"/>
-      <c r="M7" s="49"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -22088,44 +22164,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="47" t="s">
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="48"/>
-      <c r="M11" s="49"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -22208,44 +22284,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="47" t="s">
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="48"/>
-      <c r="M15" s="49"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -22407,42 +22483,42 @@
       <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -22879,26 +22955,26 @@
       <c r="L22" s="67"/>
     </row>
     <row r="23" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46" t="s">
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46" t="s">
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
@@ -23335,26 +23411,26 @@
       <c r="L41" s="67"/>
     </row>
     <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="46" t="s">
+      <c r="A42" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46" t="s">
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46" t="s">
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46" t="s">
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -23775,42 +23851,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="46"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="46"/>
-      <c r="C61" s="46"/>
-      <c r="D61" s="46" t="s">
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46" t="s">
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46" t="s">
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="46"/>
-      <c r="L61" s="46"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -24280,61 +24356,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
       <c r="M1" s="69"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="49"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="47" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="37"/>
@@ -24417,44 +24493,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="49"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
     </row>
     <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="47" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="48"/>
-      <c r="M7" s="49"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="37"/>
@@ -24537,44 +24613,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="57"/>
     </row>
     <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="47" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="47" t="s">
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="48"/>
-      <c r="M11" s="49"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="37"/>
@@ -24657,44 +24733,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="57"/>
     </row>
     <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="47" t="s">
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="48"/>
-      <c r="M15" s="49"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="37"/>

--- a/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
+++ b/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/007_POLIMO_CHAMPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21460D2B-D5E7-7141-8C0D-BE6E761E3060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA4E2BC-0CAB-5E47-ADA1-D632983DFBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -791,16 +791,34 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -815,7 +833,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,15 +851,6 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -843,21 +858,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1276,23 +1276,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
+      <c r="A2" s="52"/>
     </row>
     <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
+      <c r="A3" s="52"/>
     </row>
     <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="48"/>
+      <c r="A5" s="52"/>
     </row>
     <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1330,12 +1330,12 @@
       </c>
     </row>
     <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="53" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="49"/>
+      <c r="A14" s="53"/>
     </row>
     <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1363,12 +1363,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="52" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="48"/>
+      <c r="A21" s="52"/>
     </row>
     <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -1424,13 +1424,13 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="48" t="s">
+      <c r="A32" s="52" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="48"/>
+      <c r="A33" s="52"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1493,12 +1493,12 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="52" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="48"/>
+      <c r="A45" s="52"/>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1562,12 +1562,12 @@
       <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="48" t="s">
+      <c r="A56" s="52" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="48"/>
+      <c r="A57" s="52"/>
       <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1685,17 +1685,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -2707,36 +2707,36 @@
       <c r="AMG1" s="31"/>
     </row>
     <row r="2" spans="1:1021" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="63"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="68"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="31"/>
@@ -3748,26 +3748,26 @@
       <c r="AMG3" s="31"/>
     </row>
     <row r="4" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="54" t="s">
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54" t="s">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54" t="s">
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="21"/>
@@ -5094,20 +5094,20 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="31"/>
@@ -6119,26 +6119,26 @@
       <c r="AMG22" s="31"/>
     </row>
     <row r="23" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="54" t="s">
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54" t="s">
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
@@ -7463,20 +7463,20 @@
       <c r="L40" s="24"/>
     </row>
     <row r="41" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A41" s="67" t="s">
+      <c r="A41" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
+      <c r="L41" s="48"/>
       <c r="M41" s="31"/>
       <c r="N41" s="31"/>
       <c r="O41" s="31"/>
@@ -8488,26 +8488,26 @@
       <c r="AMG41" s="31"/>
     </row>
     <row r="42" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="54" t="s">
+      <c r="B42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54" t="s">
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="54" t="s">
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="54"/>
-      <c r="L42" s="54"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
@@ -9834,20 +9834,20 @@
       <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="67"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="67"/>
-      <c r="K60" s="67"/>
-      <c r="L60" s="67"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
+      <c r="L60" s="48"/>
       <c r="M60" s="31"/>
       <c r="N60" s="31"/>
       <c r="O60" s="31"/>
@@ -10859,26 +10859,26 @@
       <c r="AMG60" s="31"/>
     </row>
     <row r="61" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A61" s="55" t="s">
+      <c r="A61" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="56"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="54" t="s">
+      <c r="B61" s="64"/>
+      <c r="C61" s="65"/>
+      <c r="D61" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54" t="s">
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="54"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54" t="s">
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="54"/>
-      <c r="L61" s="54"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="47"/>
       <c r="M61" s="31"/>
       <c r="N61" s="31"/>
       <c r="O61" s="31"/>
@@ -12204,6 +12204,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:I42"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="D23:F23"/>
@@ -12216,16 +12226,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:I42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12249,63 +12249,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="66"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="51"/>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="63"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="68"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55" t="s">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="56"/>
-      <c r="I4" s="57"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="65"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -12509,34 +12509,34 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="63"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="68"/>
     </row>
     <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="55" t="s">
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
@@ -12740,34 +12740,34 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="63"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="68"/>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54" t="s">
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="55" t="s">
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
@@ -12971,34 +12971,34 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A36" s="61" t="s">
+      <c r="A36" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="62"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="68"/>
     </row>
     <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54" t="s">
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="55" t="s">
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="56"/>
-      <c r="I37" s="57"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="65"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
@@ -13203,12 +13203,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="D37:F37"/>
@@ -13221,6 +13215,12 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="G26:I26"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13238,12 +13238,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
     </row>
     <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
@@ -14298,12 +14298,12 @@
       <c r="AMJ3" s="10"/>
     </row>
     <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -15372,12 +15372,12 @@
       <c r="AMJ6" s="10"/>
     </row>
     <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -16446,12 +16446,12 @@
       <c r="AMJ9" s="10"/>
     </row>
     <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -17526,12 +17526,12 @@
       <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -17974,12 +17974,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18019,7 +18019,7 @@
         <v>1.7542097586549999E-2</v>
       </c>
       <c r="D3" s="11">
-        <v>4.7317405152390003E-2</v>
+        <v>-4.7317405152390003E-2</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -18027,12 +18027,12 @@
       <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="53"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="59"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
@@ -18067,7 +18067,7 @@
         <v>1.7685039776339999E-2</v>
       </c>
       <c r="D6" s="11">
-        <v>4.7474994517069997E-2</v>
+        <v>-4.7474994517069997E-2</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -18077,12 +18077,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="59"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -18121,7 +18121,7 @@
         <v>1.808727845965E-2</v>
       </c>
       <c r="D9" s="11">
-        <v>4.7553786452380002E-2</v>
+        <v>-4.7553786452380002E-2</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -18136,12 +18136,12 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="53"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="59"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -18180,7 +18180,7 @@
         <v>2.2333873933720001E-2</v>
       </c>
       <c r="D12" s="11">
-        <v>4.9474067725809999E-2</v>
+        <v>-4.9474067725809999E-2</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -18204,12 +18204,12 @@
       <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -18220,12 +18220,12 @@
       <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -18682,12 +18682,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18774,12 +18774,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="59"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
@@ -18860,12 +18860,12 @@
       <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="53"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -18957,12 +18957,12 @@
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="53"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -19065,12 +19065,12 @@
       <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="50" t="s">
+      <c r="A26" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -19081,12 +19081,12 @@
       <c r="O26" s="10"/>
     </row>
     <row r="27" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -19553,61 +19553,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="55" t="s">
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="56"/>
-      <c r="M3" s="57"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -19690,44 +19690,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="68"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55" t="s">
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="55" t="s">
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -19810,44 +19810,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55" t="s">
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="56"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="55" t="s">
+      <c r="I11" s="64"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="57"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -19930,44 +19930,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55" t="s">
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="55" t="s">
+      <c r="I15" s="64"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="56"/>
-      <c r="M15" s="57"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="65"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -20051,6 +20051,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="A2:M2"/>
@@ -20062,16 +20072,6 @@
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="K7:M7"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20099,74 +20099,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
     </row>
     <row r="2" spans="1:17" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
     </row>
     <row r="4" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54" t="s">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54" t="s">
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
@@ -20598,46 +20598,46 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
       <c r="M22" s="28"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
     </row>
     <row r="23" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54" t="s">
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54" t="s">
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
@@ -21055,45 +21055,45 @@
       <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="67" t="s">
+      <c r="A41" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
+      <c r="L41" s="48"/>
       <c r="O41" s="29"/>
       <c r="P41" s="29"/>
       <c r="Q41" s="29"/>
     </row>
     <row r="42" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54" t="s">
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54" t="s">
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="54" t="s">
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="54"/>
-      <c r="L42" s="54"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -21457,42 +21457,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="54"/>
+      <c r="B60" s="47"/>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47"/>
+      <c r="L60" s="47"/>
     </row>
     <row r="61" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54" t="s">
+      <c r="B61" s="47"/>
+      <c r="C61" s="47"/>
+      <c r="D61" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54" t="s">
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="54"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54" t="s">
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="54"/>
-      <c r="L61" s="54"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="47"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -21857,6 +21857,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A42:C42"/>
@@ -21873,12 +21879,6 @@
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="G42:I42"/>
     <mergeCell ref="J42:L42"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A3:L3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21907,61 +21907,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="62"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="55" t="s">
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="56"/>
-      <c r="M3" s="57"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -22044,44 +22044,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-      <c r="M6" s="63"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="68"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55" t="s">
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="55" t="s">
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -22164,44 +22164,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55" t="s">
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="56"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="55" t="s">
+      <c r="I11" s="64"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="57"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -22284,44 +22284,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55" t="s">
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="55" t="s">
+      <c r="I15" s="64"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="56"/>
-      <c r="M15" s="57"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="65"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -22405,12 +22405,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
@@ -22426,6 +22420,12 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22451,74 +22451,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54" t="s">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54" t="s">
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -22939,42 +22939,42 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54" t="s">
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54" t="s">
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
@@ -23395,42 +23395,42 @@
       <c r="L40" s="26"/>
     </row>
     <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="67" t="s">
+      <c r="A41" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
+      <c r="L41" s="48"/>
     </row>
     <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54" t="s">
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54" t="s">
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="54" t="s">
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="54"/>
-      <c r="L42" s="54"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -23851,42 +23851,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="54"/>
+      <c r="B60" s="47"/>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47"/>
+      <c r="L60" s="47"/>
     </row>
     <row r="61" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54" t="s">
+      <c r="B61" s="47"/>
+      <c r="C61" s="47"/>
+      <c r="D61" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54" t="s">
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="54"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54" t="s">
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="54"/>
-      <c r="L61" s="54"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="47"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -24308,13 +24308,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="G61:I61"/>
@@ -24330,6 +24323,13 @@
     <mergeCell ref="G42:I42"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="A60:L60"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24356,61 +24356,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
       <c r="M1" s="69"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="57"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="65"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="55" t="s">
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="56"/>
-      <c r="M3" s="57"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="37"/>
@@ -24493,44 +24493,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="57"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="65"/>
     </row>
     <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54" t="s">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55" t="s">
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="55" t="s">
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="37"/>
@@ -24613,44 +24613,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="57"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="65"/>
     </row>
     <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55" t="s">
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="56"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="55" t="s">
+      <c r="I11" s="64"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="57"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="37"/>
@@ -24733,44 +24733,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="57"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55" t="s">
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="55" t="s">
+      <c r="I15" s="64"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="56"/>
-      <c r="M15" s="57"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="65"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="37"/>
@@ -24854,12 +24854,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
@@ -24875,6 +24869,12 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
+++ b/007_POLIMO_CHAMPS/gridConvergence_D01_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkzayni/Desktop/UNIVERSITY/POST_PROCESS/postProcessingData/007_POLIMO_CHAMPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA4E2BC-0CAB-5E47-ADA1-D632983DFBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1DDBE7-F444-E544-B3C6-98F8917A85C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52720" yWindow="920" windowWidth="51200" windowHeight="26720" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="1" r:id="rId1"/>
@@ -791,23 +791,17 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -821,16 +815,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,15 +836,6 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -858,6 +843,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1276,23 +1276,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="52"/>
+      <c r="A2" s="50"/>
     </row>
     <row r="3" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="52"/>
+      <c r="A3" s="50"/>
     </row>
     <row r="4" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="52"/>
+      <c r="A5" s="50"/>
     </row>
     <row r="6" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1330,12 +1330,12 @@
       </c>
     </row>
     <row r="13" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="51" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="53"/>
+      <c r="A14" s="51"/>
     </row>
     <row r="15" spans="1:1" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1363,12 +1363,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="50" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="52"/>
+      <c r="A21" s="50"/>
     </row>
     <row r="22" spans="1:5" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -1424,13 +1424,13 @@
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="50" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="52"/>
+      <c r="A33" s="50"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1493,12 +1493,12 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="52" t="s">
+      <c r="A44" s="50" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="52"/>
+      <c r="A45" s="50"/>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1562,12 +1562,12 @@
       <c r="E55" s="4"/>
     </row>
     <row r="56" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="52" t="s">
+      <c r="A56" s="50" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="52"/>
+      <c r="A57" s="50"/>
       <c r="E57" s="4"/>
     </row>
     <row r="58" spans="1:5" ht="22" x14ac:dyDescent="0.2">
@@ -1685,17 +1685,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
@@ -2707,36 +2707,36 @@
       <c r="AMG1" s="31"/>
     </row>
     <row r="2" spans="1:1021" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="51"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="68"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="63"/>
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="31"/>
@@ -3748,26 +3748,26 @@
       <c r="AMG3" s="31"/>
     </row>
     <row r="4" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="56"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
       <c r="O4" s="21"/>
@@ -5094,20 +5094,20 @@
       <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
       <c r="M22" s="33"/>
       <c r="N22" s="33"/>
       <c r="O22" s="31"/>
@@ -6119,26 +6119,26 @@
       <c r="AMG22" s="31"/>
     </row>
     <row r="23" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="47" t="s">
+      <c r="B23" s="56"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47" t="s">
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
       <c r="M23" s="31"/>
       <c r="N23" s="31"/>
       <c r="O23" s="31"/>
@@ -7463,20 +7463,20 @@
       <c r="L40" s="24"/>
     </row>
     <row r="41" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
-      <c r="L41" s="48"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
       <c r="M41" s="31"/>
       <c r="N41" s="31"/>
       <c r="O41" s="31"/>
@@ -8488,26 +8488,26 @@
       <c r="AMG41" s="31"/>
     </row>
     <row r="42" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A42" s="63" t="s">
+      <c r="A42" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="64"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="47" t="s">
+      <c r="B42" s="56"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47" t="s">
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47" t="s">
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
       <c r="M42" s="31"/>
       <c r="N42" s="31"/>
       <c r="O42" s="31"/>
@@ -9834,20 +9834,20 @@
       <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="48"/>
-      <c r="C60" s="48"/>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
-      <c r="L60" s="48"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="67"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="67"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="67"/>
       <c r="M60" s="31"/>
       <c r="N60" s="31"/>
       <c r="O60" s="31"/>
@@ -10859,26 +10859,26 @@
       <c r="AMG60" s="31"/>
     </row>
     <row r="61" spans="1:1021" s="32" customFormat="1" ht="27" x14ac:dyDescent="0.35">
-      <c r="A61" s="63" t="s">
+      <c r="A61" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="64"/>
-      <c r="C61" s="65"/>
-      <c r="D61" s="47" t="s">
+      <c r="B61" s="56"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47" t="s">
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="47"/>
-      <c r="I61" s="47"/>
-      <c r="J61" s="47" t="s">
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="47"/>
-      <c r="L61" s="47"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
       <c r="M61" s="31"/>
       <c r="N61" s="31"/>
       <c r="O61" s="31"/>
@@ -12204,16 +12204,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G42:I42"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="D23:F23"/>
@@ -12226,6 +12216,16 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="G42:I42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12249,63 +12249,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="66"/>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
       <c r="L2" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="68"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="63" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="64"/>
-      <c r="I4" s="65"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -12509,34 +12509,34 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="68"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="63" t="s">
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
@@ -12740,34 +12740,34 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="63"/>
     </row>
     <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47" t="s">
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="63" t="s">
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
@@ -12971,34 +12971,34 @@
       <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="67"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="68"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A37" s="47" t="s">
+      <c r="A37" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47" t="s">
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="63" t="s">
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="H37" s="64"/>
-      <c r="I37" s="65"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
@@ -13203,6 +13203,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="D37:F37"/>
@@ -13215,12 +13221,6 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13238,12 +13238,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
     </row>
     <row r="2" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
@@ -13274,7 +13274,7 @@
         <v>1.290927168187E-2</v>
       </c>
       <c r="D3" s="11">
-        <v>2.2130249579159999E-2</v>
+        <v>-1.2840174168320001E-3</v>
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
@@ -14298,12 +14298,12 @@
       <c r="AMJ3" s="10"/>
     </row>
     <row r="4" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="J4" s="7"/>
@@ -14348,7 +14348,7 @@
         <v>1.358100670772E-2</v>
       </c>
       <c r="D6" s="11">
-        <v>2.328175950868E-2</v>
+        <v>-6.1487253271829995E-4</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -15372,12 +15372,12 @@
       <c r="AMJ6" s="10"/>
     </row>
     <row r="7" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="J7" s="7"/>
@@ -15419,10 +15419,10 @@
         <v>0.465248328727</v>
       </c>
       <c r="C9" s="38">
-        <v>5.6574475149399998E-3</v>
+        <v>1.5657447514939998E-2</v>
       </c>
       <c r="D9" s="38">
-        <v>2.6841355741140001E-2</v>
+        <v>-4.3294112857550002E-4</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -16446,12 +16446,12 @@
       <c r="AMJ9" s="10"/>
     </row>
     <row r="10" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
       <c r="G10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -16493,7 +16493,7 @@
         <v>1.6791354190239999E-2</v>
       </c>
       <c r="D12" s="11">
-        <v>2.8787532449549999E-2</v>
+        <v>-4.3331075234609998E-4</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -17526,12 +17526,12 @@
       <c r="R13" s="7"/>
     </row>
     <row r="14" spans="1:1024" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -17974,12 +17974,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18027,12 +18027,12 @@
       <c r="O3" s="10"/>
     </row>
     <row r="4" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="59"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="49"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="I4" s="10"/>
@@ -18077,12 +18077,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="59"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -18136,12 +18136,12 @@
       <c r="O9" s="10"/>
     </row>
     <row r="10" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="59"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="I10" s="10"/>
@@ -18174,7 +18174,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="11">
-        <v>0.12562352199410001</v>
+        <v>0.12562334570229999</v>
       </c>
       <c r="C12" s="11">
         <v>2.2333873933720001E-2</v>
@@ -18204,12 +18204,12 @@
       <c r="O13" s="10"/>
     </row>
     <row r="14" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -18220,12 +18220,12 @@
       <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:18" s="9" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -18682,12 +18682,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
@@ -18774,12 +18774,12 @@
       <c r="O6" s="10"/>
     </row>
     <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="59"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="I7" s="10"/>
@@ -18860,12 +18860,12 @@
       <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:18" ht="27" x14ac:dyDescent="0.2">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -18957,12 +18957,12 @@
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="59"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="I19" s="10"/>
@@ -19065,12 +19065,12 @@
       <c r="O25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -19081,12 +19081,12 @@
       <c r="O26" s="10"/>
     </row>
     <row r="27" spans="1:15" ht="27" x14ac:dyDescent="0.2">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -19553,61 +19553,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="62"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="63" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="63" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="65"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -19690,44 +19690,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="63" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="63" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -19810,44 +19810,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="63" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="63" t="s">
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -19930,44 +19930,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="63" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="63" t="s">
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="64"/>
-      <c r="M15" s="65"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -20051,16 +20051,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K11:M11"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="A2:M2"/>
@@ -20072,6 +20062,16 @@
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="K7:M7"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20099,74 +20099,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
     </row>
     <row r="2" spans="1:17" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="51"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
@@ -20598,46 +20598,46 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
       <c r="M22" s="28"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
     </row>
     <row r="23" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47" t="s">
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47" t="s">
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
@@ -21055,45 +21055,45 @@
       <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
-      <c r="L41" s="48"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
       <c r="O41" s="29"/>
       <c r="P41" s="29"/>
       <c r="Q41" s="29"/>
     </row>
     <row r="42" spans="1:17" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="47" t="s">
+      <c r="A42" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47" t="s">
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47" t="s">
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47" t="s">
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -21457,42 +21457,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="47"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="47"/>
-      <c r="J60" s="47"/>
-      <c r="K60" s="47"/>
-      <c r="L60" s="47"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="1:12" s="27" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="47"/>
-      <c r="C61" s="47"/>
-      <c r="D61" s="47" t="s">
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47" t="s">
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="47"/>
-      <c r="I61" s="47"/>
-      <c r="J61" s="47" t="s">
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="47"/>
-      <c r="L61" s="47"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -21857,12 +21857,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A60:L60"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A42:C42"/>
@@ -21879,6 +21873,12 @@
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="G42:I42"/>
     <mergeCell ref="J42:L42"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A60:L60"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A3:L3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21907,61 +21907,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="62"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="60"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="63" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="63" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="65"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="17"/>
@@ -22044,44 +22044,44 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
     </row>
     <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="63" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="63" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -22164,44 +22164,44 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
     </row>
     <row r="11" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="63" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="63" t="s">
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
@@ -22284,44 +22284,44 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
     </row>
     <row r="15" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="63" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="63" t="s">
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="64"/>
-      <c r="M15" s="65"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
@@ -22405,6 +22405,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
@@ -22420,12 +22426,6 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22451,74 +22451,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
     </row>
     <row r="2" spans="1:12" s="6" customFormat="1" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="51"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
@@ -22939,42 +22939,42 @@
       <c r="L21" s="26"/>
     </row>
     <row r="22" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
     </row>
     <row r="23" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47" t="s">
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47" t="s">
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47" t="s">
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
@@ -23395,42 +23395,42 @@
       <c r="L40" s="26"/>
     </row>
     <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
-      <c r="L41" s="48"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
     </row>
     <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A42" s="47" t="s">
+      <c r="A42" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47" t="s">
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47" t="s">
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47" t="s">
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
@@ -23851,42 +23851,42 @@
       <c r="L59" s="26"/>
     </row>
     <row r="60" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="47"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="47"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="47"/>
-      <c r="J60" s="47"/>
-      <c r="K60" s="47"/>
-      <c r="L60" s="47"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="47"/>
-      <c r="C61" s="47"/>
-      <c r="D61" s="47" t="s">
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47" t="s">
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="47"/>
-      <c r="I61" s="47"/>
-      <c r="J61" s="47" t="s">
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="47"/>
-      <c r="L61" s="47"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
@@ -24308,6 +24308,13 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="G61:I61"/>
@@ -24323,13 +24330,6 @@
     <mergeCell ref="G42:I42"/>
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="A60:L60"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24356,61 +24356,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
       <c r="M1" s="69"/>
     </row>
     <row r="2" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="65"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="63" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="63" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="64"/>
-      <c r="M3" s="65"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="37"/>
@@ -24459,78 +24459,78 @@
         <v>3.2373830603</v>
       </c>
       <c r="C5" s="44">
-        <v>2.7366929923000001</v>
+        <v>2.8264798010000001</v>
       </c>
       <c r="D5" s="44">
-        <v>0.40949689586999999</v>
+        <v>0.33718386946000001</v>
       </c>
       <c r="E5" s="44">
-        <v>3.6984009884E-3</v>
+        <v>3.2087972661999999</v>
       </c>
       <c r="F5" s="44">
-        <v>3.1263097821999999E-3</v>
+        <v>2.7976518139</v>
       </c>
       <c r="G5" s="44">
-        <v>4.6986646955999998E-4</v>
+        <v>0.33922889624000002</v>
       </c>
       <c r="H5" s="44">
         <v>3.1974199529999998</v>
       </c>
       <c r="I5" s="44">
-        <v>2.7027885705000001</v>
+        <v>2.7853946509999998</v>
       </c>
       <c r="J5" s="44">
-        <v>0.40642867326999998</v>
+        <v>0.34151542361999998</v>
       </c>
       <c r="K5" s="44">
         <v>3.1911245305999998</v>
       </c>
       <c r="L5" s="44">
-        <v>2.6973362806000001</v>
+        <v>2.7792825578999998</v>
       </c>
       <c r="M5" s="44">
-        <v>0.40554608757999999</v>
+        <v>0.34152307138999999</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="65"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="57"/>
     </row>
     <row r="7" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="63" t="s">
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="63" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="37"/>
@@ -24579,78 +24579,78 @@
         <v>3.2401451341</v>
       </c>
       <c r="C9" s="44">
-        <v>2.7187869164</v>
+        <v>2.8114500231999999</v>
       </c>
       <c r="D9" s="44">
-        <v>0.39530567837000002</v>
+        <v>0.32601204952000001</v>
       </c>
       <c r="E9" s="11">
         <v>3.2115544184</v>
       </c>
       <c r="F9" s="11">
-        <v>2.6957408318999998</v>
+        <v>2.7828099296</v>
       </c>
       <c r="G9" s="11">
-        <v>0.39153004123000001</v>
+        <v>0.33067357472999998</v>
       </c>
       <c r="H9" s="11">
         <v>3.2001632531999999</v>
       </c>
       <c r="I9" s="38">
-        <v>2.6855553951000002</v>
+        <v>2.7714475734000001</v>
       </c>
       <c r="J9" s="38">
-        <v>0.39184263867000002</v>
+        <v>0.33201212869000002</v>
       </c>
       <c r="K9" s="25">
         <v>3.1939341859999999</v>
       </c>
       <c r="L9" s="25">
-        <v>2.6801451601999999</v>
+        <v>2.7651896565</v>
       </c>
       <c r="M9" s="25">
-        <v>0.39122127636999998</v>
+        <v>0.33266638480999999</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="65"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="57"/>
     </row>
     <row r="11" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47" t="s">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="63" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="63" t="s">
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="57"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="37"/>
@@ -24699,78 +24699,78 @@
         <v>3.2428162039999999</v>
       </c>
       <c r="C13" s="44">
-        <v>2.6975520166</v>
+        <v>2.7975970938999999</v>
       </c>
       <c r="D13" s="44">
-        <v>0.37958422967</v>
+        <v>0.31420122379999998</v>
       </c>
       <c r="E13" s="11">
         <v>3.2141247582000001</v>
       </c>
       <c r="F13" s="11">
-        <v>2.6761669964000001</v>
+        <v>2.771663137</v>
       </c>
       <c r="G13" s="11">
-        <v>0.37590581593</v>
+        <v>0.31448632399999998</v>
       </c>
       <c r="H13" s="11">
         <v>3.2032371215</v>
       </c>
       <c r="I13" s="11">
-        <v>2.6684890567999999</v>
+        <v>2.7615887656</v>
       </c>
       <c r="J13" s="11">
-        <v>0.37344012843000002</v>
+        <v>0.31176240259999999</v>
       </c>
       <c r="K13" s="25">
         <v>3.1966800135</v>
       </c>
       <c r="L13" s="39">
-        <v>2.6633863251999998</v>
+        <v>2.7548389950000001</v>
       </c>
       <c r="M13" s="39">
-        <v>0.36987431354</v>
+        <v>0.31356733081999999</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="65"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="57"/>
     </row>
     <row r="15" spans="1:13" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="63" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="63" t="s">
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="64"/>
-      <c r="M15" s="65"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="57"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="37"/>
@@ -24816,44 +24816,50 @@
         <v>55</v>
       </c>
       <c r="B17" s="44">
-        <v>3.2181815744</v>
+        <v>3.2181793329000001</v>
       </c>
       <c r="C17" s="44">
-        <v>2.6427847710000001</v>
+        <v>2.7395128202999999</v>
       </c>
       <c r="D17" s="44">
-        <v>0.32328229784000001</v>
+        <v>0.30276755641999997</v>
       </c>
       <c r="E17" s="11">
-        <v>3.1928874411999999</v>
+        <v>3.1928851480999998</v>
       </c>
       <c r="F17" s="11">
-        <v>2.6249467010999998</v>
+        <v>2.7247117743000002</v>
       </c>
       <c r="G17" s="41">
-        <v>0.31956957308</v>
+        <v>0.29763860019999999</v>
       </c>
       <c r="H17" s="11">
-        <v>3.1861007111999999</v>
+        <v>3.1861002144000001</v>
       </c>
       <c r="I17" s="11">
-        <v>2.6209879303000001</v>
+        <v>2.7208708099000001</v>
       </c>
       <c r="J17" s="11">
-        <v>0.31833875262</v>
+        <v>0.29664964437000002</v>
       </c>
       <c r="K17" s="11">
-        <v>3.1803091379000001</v>
+        <v>3.1803019103999999</v>
       </c>
       <c r="L17" s="11">
-        <v>2.6161461851999999</v>
+        <v>2.7170637504999999</v>
       </c>
       <c r="M17" s="11">
-        <v>0.31858931738000001</v>
+        <v>0.29541313782</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
@@ -24869,12 +24875,6 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
